--- a/backdata.xlsx
+++ b/backdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AD0883\AI\영업대쉬보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6971F120-C8C0-4D81-982E-6A05CB0AA516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D8AD6F-EE50-4AAB-A698-29E87D77D1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="361">
   <si>
     <t>1월</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1134,12 +1134,6 @@
     <t>합계</t>
   </si>
   <si>
-    <t>(전년22%)</t>
-  </si>
-  <si>
-    <t>(전년42%)</t>
-  </si>
-  <si>
     <t>RF+도매</t>
   </si>
   <si>
@@ -1149,19 +1143,7 @@
     <t>백화점</t>
   </si>
   <si>
-    <t>(전년29%)</t>
-  </si>
-  <si>
-    <t>(전년52%)</t>
-  </si>
-  <si>
     <t>대리점</t>
-  </si>
-  <si>
-    <t>(전년20%)</t>
-  </si>
-  <si>
-    <t>(전년39%)</t>
   </si>
   <si>
     <t>온라인</t>
@@ -1180,7 +1162,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1282,8 +1264,23 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1329,6 +1326,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDCFD6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1489,7 +1492,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1639,11 +1642,85 @@
     <xf numFmtId="9" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1654,7 +1731,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1666,88 +1743,19 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2327,6 +2335,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A8293F-5038-4A8B-8ADC-B11E7F68429B}">
   <dimension ref="A2:BA5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="47" max="48" width="11.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:53" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
@@ -2467,7 +2478,7 @@
       <c r="AU2" t="s">
         <v>62</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AV2" s="54" t="s">
         <v>63</v>
       </c>
       <c r="AW2" t="s">
@@ -2628,6 +2639,9 @@
       <c r="AU3">
         <v>7283929073</v>
       </c>
+      <c r="AV3" s="54">
+        <v>7814770263</v>
+      </c>
     </row>
     <row r="4" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -2771,7 +2785,7 @@
       <c r="AU4">
         <v>6993007565</v>
       </c>
-      <c r="AV4">
+      <c r="AV4" s="54">
         <v>7212765468</v>
       </c>
       <c r="AW4">
@@ -2978,9 +2992,9 @@
         <f t="shared" si="0"/>
         <v>4.1601772241182999E-2</v>
       </c>
-      <c r="AV5" s="7">
+      <c r="AV5" s="55">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>8.3463797300888487E-2</v>
       </c>
       <c r="AW5" s="7">
         <f t="shared" si="0"/>
@@ -3006,6 +3020,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7876,70 +7891,70 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="81" t="s">
         <v>340</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="83" t="s">
         <v>341</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="16"/>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
       <c r="Q1" s="17"/>
-      <c r="R1" s="59" t="s">
+      <c r="R1" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="60" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="86" t="s">
         <v>343</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="F2" s="62" t="s">
+      <c r="F2" s="72" t="s">
         <v>347</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="72"/>
+      <c r="I2" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="K2" s="62" t="s">
+      <c r="K2" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="L2" s="62" t="s">
+      <c r="L2" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="M2" s="62" t="s">
+      <c r="M2" s="72" t="s">
         <v>347</v>
       </c>
       <c r="N2" s="18" t="s">
@@ -7948,51 +7963,51 @@
       <c r="O2" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="P2" s="62" t="s">
+      <c r="P2" s="72" t="s">
         <v>351</v>
       </c>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="62" t="s">
+      <c r="Q2" s="80"/>
+      <c r="R2" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="S2" s="62" t="s">
+      <c r="S2" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="T2" s="62" t="s">
+      <c r="T2" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="U2" s="62" t="s">
+      <c r="U2" s="72" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="56"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
       <c r="G3" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="H3" s="62"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
       <c r="N3" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O3" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
     </row>
     <row r="4" spans="1:21" ht="24" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
@@ -8002,142 +8017,142 @@
         <v>315598</v>
       </c>
       <c r="C4" s="22">
-        <v>289065</v>
+        <v>296877</v>
       </c>
       <c r="D4" s="22">
-        <v>301329</v>
+        <v>308397</v>
       </c>
       <c r="E4" s="23">
-        <v>-0.04</v>
+        <f>C4/D4-1</f>
+        <v>-3.7354448973239029E-2</v>
       </c>
       <c r="F4" s="24">
-        <v>0.92</v>
+        <f>C4/B4</f>
+        <v>0.94068086616518487</v>
       </c>
       <c r="G4" s="23">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="25">
         <v>33000</v>
       </c>
       <c r="J4" s="25">
-        <v>18087</v>
+        <v>25902</v>
       </c>
       <c r="K4" s="25">
-        <v>16739</v>
+        <v>23809</v>
       </c>
       <c r="L4" s="26">
-        <v>0.08</v>
+        <f>J4/K4-1</f>
+        <v>8.7907933974547436E-2</v>
       </c>
       <c r="M4" s="26">
-        <v>0.55000000000000004</v>
+        <f>J4/I4</f>
+        <v>0.78490909090909089</v>
       </c>
       <c r="N4" s="26">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="O4" s="27"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="28">
-        <v>7283</v>
+        <v>7814</v>
       </c>
       <c r="S4" s="28">
-        <v>6993</v>
+        <v>7212</v>
       </c>
       <c r="T4" s="29">
-        <v>0.04</v>
+        <f>R4/S4-1</f>
+        <v>8.3471991125901202E-2</v>
       </c>
       <c r="U4" s="30"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
-        <v>270</v>
-      </c>
-      <c r="B5" s="67">
+      <c r="A5" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="75">
         <v>167559</v>
       </c>
-      <c r="C5" s="69">
-        <v>146387</v>
-      </c>
-      <c r="D5" s="69">
-        <v>151119</v>
-      </c>
-      <c r="E5" s="71">
-        <v>-0.03</v>
-      </c>
-      <c r="F5" s="73">
-        <v>0.87</v>
-      </c>
-      <c r="G5" s="71">
-        <v>-0.02</v>
-      </c>
-      <c r="H5" s="62"/>
-      <c r="I5" s="69">
+      <c r="C5" s="61">
+        <v>150845</v>
+      </c>
+      <c r="D5" s="61">
+        <v>155417</v>
+      </c>
+      <c r="E5" s="62">
+        <f>C5/D5-1</f>
+        <v>-2.9417631275857836E-2</v>
+      </c>
+      <c r="F5" s="64">
+        <f>C5/B5</f>
+        <v>0.90025006117248252</v>
+      </c>
+      <c r="G5" s="62">
+        <v>0</v>
+      </c>
+      <c r="H5" s="72"/>
+      <c r="I5" s="61">
         <v>18249</v>
       </c>
-      <c r="J5" s="69">
-        <v>9878</v>
-      </c>
-      <c r="K5" s="69">
-        <v>8690</v>
-      </c>
-      <c r="L5" s="73">
+      <c r="J5" s="61">
+        <v>14335</v>
+      </c>
+      <c r="K5" s="61">
+        <v>12988</v>
+      </c>
+      <c r="L5" s="64">
+        <f>J5/K5-1</f>
+        <v>0.1037111179550354</v>
+      </c>
+      <c r="M5" s="64">
+        <f>J5/I5</f>
+        <v>0.78552249438325383</v>
+      </c>
+      <c r="N5" s="64">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M5" s="73">
-        <v>0.54</v>
-      </c>
-      <c r="N5" s="73">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="O5" s="75">
-        <v>-0.05</v>
-      </c>
-      <c r="P5" s="34">
-        <v>0.35</v>
-      </c>
-      <c r="Q5" s="77">
+      <c r="O5" s="78"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="59">
         <v>0.22</v>
       </c>
-      <c r="R5" s="69">
-        <v>3711</v>
-      </c>
-      <c r="S5" s="69">
-        <v>3746</v>
-      </c>
-      <c r="T5" s="71">
-        <v>-0.01</v>
-      </c>
-      <c r="U5" s="34">
-        <v>0.22</v>
-      </c>
+      <c r="R5" s="61">
+        <v>4457</v>
+      </c>
+      <c r="S5" s="61">
+        <v>4412</v>
+      </c>
+      <c r="T5" s="88">
+        <f>R5/S5-1</f>
+        <v>1.0199456029011733E-2</v>
+      </c>
+      <c r="U5" s="34"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="66"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="68"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="16" t="s">
-        <v>355</v>
-      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="60"/>
+      <c r="S6" s="60"/>
+      <c r="T6" s="89"/>
+      <c r="U6" s="16"/>
     </row>
     <row r="7" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
@@ -8147,71 +8162,78 @@
         <v>108496</v>
       </c>
       <c r="C7" s="31">
-        <v>103899</v>
+        <v>106425</v>
       </c>
       <c r="D7" s="31">
-        <v>120793</v>
+        <v>122900</v>
       </c>
       <c r="E7" s="32">
-        <v>-0.14000000000000001</v>
+        <f>C7/D7-1</f>
+        <v>-0.13405207485760784</v>
       </c>
       <c r="F7" s="33">
-        <v>0.96</v>
+        <f>C7/B7</f>
+        <v>0.98091173868161041</v>
       </c>
       <c r="G7" s="32">
-        <v>-0.08</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="H7" s="18"/>
       <c r="I7" s="31">
         <v>10600</v>
       </c>
       <c r="J7" s="31">
-        <v>5854</v>
+        <v>8382</v>
       </c>
       <c r="K7" s="31">
-        <v>6378</v>
+        <v>8486</v>
       </c>
       <c r="L7" s="32">
-        <v>-0.08</v>
+        <f>J7/K7-1</f>
+        <v>-1.2255479613481057E-2</v>
       </c>
       <c r="M7" s="33">
-        <v>0.55000000000000004</v>
+        <f>J7/I7</f>
+        <v>0.79075471698113209</v>
       </c>
       <c r="N7" s="33">
-        <v>0.03</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O7" s="18"/>
       <c r="P7" s="18"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="31">
-        <v>2648</v>
+        <v>2528</v>
       </c>
       <c r="S7" s="31">
-        <v>2539</v>
+        <v>2136</v>
       </c>
       <c r="T7" s="33">
-        <v>0.04</v>
+        <f>R7/S7-1</f>
+        <v>0.18352059925093633</v>
       </c>
       <c r="U7" s="17"/>
     </row>
     <row r="8" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B8" s="36">
         <v>39543</v>
       </c>
       <c r="C8" s="31">
-        <v>38779</v>
+        <v>39607</v>
       </c>
       <c r="D8" s="31">
-        <v>29417</v>
+        <v>30079</v>
       </c>
       <c r="E8" s="33">
-        <v>0.32</v>
+        <f>C8/D8-1</f>
+        <v>0.31676584992852153</v>
       </c>
       <c r="F8" s="33">
-        <v>0.98</v>
+        <f>C8/B8</f>
+        <v>1.001618491262676</v>
       </c>
       <c r="G8" s="33">
         <v>0.14000000000000001</v>
@@ -8221,16 +8243,18 @@
         <v>4151</v>
       </c>
       <c r="J8" s="31">
-        <v>2356</v>
+        <v>3184</v>
       </c>
       <c r="K8" s="31">
-        <v>1671</v>
+        <v>2334</v>
       </c>
       <c r="L8" s="33">
-        <v>0.41</v>
+        <f>J8/K8-1</f>
+        <v>0.36418166238217653</v>
       </c>
       <c r="M8" s="33">
-        <v>0.56999999999999995</v>
+        <f>J8/I8</f>
+        <v>0.76704408576246685</v>
       </c>
       <c r="N8" s="33">
         <v>0.12</v>
@@ -8239,13 +8263,14 @@
       <c r="P8" s="18"/>
       <c r="Q8" s="17"/>
       <c r="R8" s="18">
-        <v>924</v>
+        <v>828</v>
       </c>
       <c r="S8" s="18">
-        <v>708</v>
+        <v>663</v>
       </c>
       <c r="T8" s="33">
-        <v>0.31</v>
+        <f>R8/S8-1</f>
+        <v>0.24886877828054299</v>
       </c>
       <c r="U8" s="17"/>
     </row>
@@ -8273,70 +8298,70 @@
       <c r="U9" s="17"/>
     </row>
     <row r="10" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="55" t="s">
-        <v>357</v>
-      </c>
-      <c r="B10" s="57" t="s">
+      <c r="A10" s="81" t="s">
+        <v>355</v>
+      </c>
+      <c r="B10" s="83" t="s">
         <v>341</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
       <c r="H10" s="16"/>
-      <c r="I10" s="59" t="s">
+      <c r="I10" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="59"/>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="59"/>
-      <c r="N10" s="59"/>
-      <c r="O10" s="59"/>
-      <c r="P10" s="59"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="85"/>
       <c r="Q10" s="17"/>
-      <c r="R10" s="59" t="s">
+      <c r="R10" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="S10" s="59"/>
-      <c r="T10" s="59"/>
-      <c r="U10" s="59"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="85"/>
+      <c r="U10" s="85"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="55"/>
-      <c r="B11" s="60" t="s">
+      <c r="A11" s="81"/>
+      <c r="B11" s="86" t="s">
         <v>343</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="D11" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="E11" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="F11" s="72" t="s">
         <v>347</v>
       </c>
       <c r="G11" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="H11" s="78"/>
-      <c r="I11" s="62" t="s">
+      <c r="H11" s="71"/>
+      <c r="I11" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="J11" s="62" t="s">
+      <c r="J11" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="K11" s="62" t="s">
+      <c r="K11" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="L11" s="62" t="s">
+      <c r="L11" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="M11" s="62" t="s">
+      <c r="M11" s="72" t="s">
         <v>347</v>
       </c>
       <c r="N11" s="18" t="s">
@@ -8345,51 +8370,51 @@
       <c r="O11" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="P11" s="62" t="s">
+      <c r="P11" s="72" t="s">
         <v>351</v>
       </c>
-      <c r="Q11" s="64"/>
-      <c r="R11" s="62" t="s">
+      <c r="Q11" s="80"/>
+      <c r="R11" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="S11" s="62" t="s">
+      <c r="S11" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="T11" s="62" t="s">
+      <c r="T11" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="U11" s="62" t="s">
+      <c r="U11" s="72" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="56"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
       <c r="G12" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="H12" s="78"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
       <c r="N12" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O12" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="P12" s="63"/>
-      <c r="Q12" s="64"/>
-      <c r="R12" s="63"/>
-      <c r="S12" s="63"/>
-      <c r="T12" s="63"/>
-      <c r="U12" s="63"/>
+      <c r="P12" s="73"/>
+      <c r="Q12" s="80"/>
+      <c r="R12" s="73"/>
+      <c r="S12" s="73"/>
+      <c r="T12" s="73"/>
+      <c r="U12" s="73"/>
     </row>
     <row r="13" spans="1:21" ht="24" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
@@ -8399,342 +8424,346 @@
         <v>315598</v>
       </c>
       <c r="C13" s="22">
-        <v>289062</v>
+        <v>296877</v>
       </c>
       <c r="D13" s="22">
-        <v>301327</v>
+        <v>308397</v>
       </c>
       <c r="E13" s="23">
-        <v>-0.04</v>
+        <f>C13/D13-1</f>
+        <v>-3.7354448973239029E-2</v>
       </c>
       <c r="F13" s="24">
-        <v>0.92</v>
+        <f>C13/B13</f>
+        <v>0.94068086616518487</v>
       </c>
       <c r="G13" s="39">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="25">
         <v>33000</v>
       </c>
       <c r="J13" s="25">
-        <v>18087</v>
+        <v>25902</v>
       </c>
       <c r="K13" s="25">
-        <v>16739</v>
+        <v>23809</v>
       </c>
       <c r="L13" s="26">
-        <v>0.08</v>
+        <f>J13/K13-1</f>
+        <v>8.7907933974547436E-2</v>
       </c>
       <c r="M13" s="26">
-        <v>0.55000000000000004</v>
+        <f>J13/I13</f>
+        <v>0.78490909090909089</v>
       </c>
       <c r="N13" s="26">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="O13" s="27"/>
       <c r="P13" s="27"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="28">
-        <v>7283</v>
+        <v>7814</v>
       </c>
       <c r="S13" s="28">
-        <v>6993</v>
+        <v>7212</v>
       </c>
       <c r="T13" s="29">
-        <v>0.04</v>
+        <f>R13/S13-1</f>
+        <v>8.3471991125901202E-2</v>
       </c>
       <c r="U13" s="30"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="65" t="s">
-        <v>358</v>
-      </c>
-      <c r="B14" s="67">
+      <c r="A14" s="74" t="s">
+        <v>356</v>
+      </c>
+      <c r="B14" s="75">
         <v>81716</v>
       </c>
-      <c r="C14" s="69">
-        <v>74087</v>
-      </c>
-      <c r="D14" s="69">
-        <v>75346</v>
-      </c>
-      <c r="E14" s="79">
-        <v>-0.02</v>
-      </c>
-      <c r="F14" s="73">
-        <v>0.91</v>
-      </c>
-      <c r="G14" s="75">
-        <v>-0.01</v>
-      </c>
-      <c r="H14" s="78"/>
-      <c r="I14" s="69">
+      <c r="C14" s="61">
+        <v>76086</v>
+      </c>
+      <c r="D14" s="61">
+        <v>77288</v>
+      </c>
+      <c r="E14" s="76">
+        <f>C14/D14-1</f>
+        <v>-1.5552220267053052E-2</v>
+      </c>
+      <c r="F14" s="64">
+        <f>C14/B14</f>
+        <v>0.93110284399627985</v>
+      </c>
+      <c r="G14" s="90">
+        <v>0.01</v>
+      </c>
+      <c r="H14" s="71"/>
+      <c r="I14" s="61">
         <v>8970</v>
       </c>
-      <c r="J14" s="69">
-        <v>4905</v>
-      </c>
-      <c r="K14" s="69">
-        <v>4598</v>
-      </c>
-      <c r="L14" s="73">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="M14" s="81">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="N14" s="73">
-        <v>0.02</v>
-      </c>
-      <c r="O14" s="83">
-        <v>-0.12</v>
-      </c>
-      <c r="P14" s="42">
-        <v>0.42</v>
-      </c>
-      <c r="Q14" s="77">
+      <c r="J14" s="61">
+        <v>6904</v>
+      </c>
+      <c r="K14" s="61">
+        <v>6540</v>
+      </c>
+      <c r="L14" s="64">
+        <f>J14/K14-1</f>
+        <v>5.5657492354740157E-2</v>
+      </c>
+      <c r="M14" s="70">
+        <f>J14/I14</f>
+        <v>0.7696767001114827</v>
+      </c>
+      <c r="N14" s="64">
+        <v>0.11</v>
+      </c>
+      <c r="O14" s="65"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="59">
         <v>0.28999999999999998</v>
       </c>
-      <c r="R14" s="69">
-        <v>1685</v>
-      </c>
-      <c r="S14" s="69">
-        <v>1943</v>
-      </c>
-      <c r="T14" s="71">
-        <v>-0.13</v>
-      </c>
-      <c r="U14" s="42">
-        <v>0.34</v>
-      </c>
+      <c r="R14" s="61">
+        <v>1998</v>
+      </c>
+      <c r="S14" s="61">
+        <v>2007</v>
+      </c>
+      <c r="T14" s="62">
+        <f>R14/S14-1</f>
+        <v>-4.484304932735439E-3</v>
+      </c>
+      <c r="U14" s="42"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="66"/>
+      <c r="A15" s="67"/>
       <c r="B15" s="68"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="41" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q15" s="77"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="70"/>
-      <c r="T15" s="72"/>
-      <c r="U15" s="41" t="s">
-        <v>360</v>
-      </c>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="59"/>
+      <c r="R15" s="60"/>
+      <c r="S15" s="60"/>
+      <c r="T15" s="63"/>
+      <c r="U15" s="41"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="66" t="s">
-        <v>361</v>
+      <c r="A16" s="67" t="s">
+        <v>357</v>
       </c>
       <c r="B16" s="68">
         <v>56159</v>
       </c>
-      <c r="C16" s="85">
-        <v>52053</v>
-      </c>
-      <c r="D16" s="85">
-        <v>50912</v>
-      </c>
-      <c r="E16" s="86">
+      <c r="C16" s="60">
+        <v>50485</v>
+      </c>
+      <c r="D16" s="60">
+        <v>49355</v>
+      </c>
+      <c r="E16" s="69">
         <v>0.02</v>
       </c>
-      <c r="F16" s="87">
-        <v>0.93</v>
-      </c>
-      <c r="G16" s="88">
-        <v>0.05</v>
-      </c>
-      <c r="H16" s="78"/>
-      <c r="I16" s="85">
+      <c r="F16" s="56">
+        <f>C16/D16-1</f>
+        <v>2.2895350015196048E-2</v>
+      </c>
+      <c r="G16" s="57">
+        <v>0.06</v>
+      </c>
+      <c r="H16" s="71"/>
+      <c r="I16" s="60">
         <v>6260</v>
       </c>
-      <c r="J16" s="85">
-        <v>3795</v>
-      </c>
-      <c r="K16" s="85">
-        <v>2861</v>
-      </c>
-      <c r="L16" s="87">
-        <v>0.33</v>
-      </c>
-      <c r="M16" s="88">
-        <v>0.61</v>
-      </c>
-      <c r="N16" s="87">
-        <v>0.23</v>
-      </c>
-      <c r="O16" s="89">
-        <v>0.04</v>
-      </c>
-      <c r="P16" s="40">
-        <v>0.37</v>
-      </c>
-      <c r="Q16" s="77">
+      <c r="J16" s="60">
+        <v>4892</v>
+      </c>
+      <c r="K16" s="60">
+        <v>4179</v>
+      </c>
+      <c r="L16" s="56">
+        <f>J16/K16-1</f>
+        <v>0.17061497966020589</v>
+      </c>
+      <c r="M16" s="57">
+        <f>J16/I16</f>
+        <v>0.78146964856230028</v>
+      </c>
+      <c r="N16" s="56">
+        <v>0.17</v>
+      </c>
+      <c r="O16" s="58"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="59">
         <v>0.2</v>
       </c>
-      <c r="R16" s="85">
-        <v>1414</v>
-      </c>
-      <c r="S16" s="85">
-        <v>1207</v>
-      </c>
-      <c r="T16" s="87">
-        <v>0.17</v>
-      </c>
-      <c r="U16" s="40">
-        <v>0.32</v>
-      </c>
+      <c r="R16" s="60">
+        <v>1273</v>
+      </c>
+      <c r="S16" s="60">
+        <v>1479</v>
+      </c>
+      <c r="T16" s="56">
+        <f>R16/S16-1</f>
+        <v>-0.13928329952670726</v>
+      </c>
+      <c r="U16" s="40"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="66"/>
+      <c r="A17" s="67"/>
       <c r="B17" s="68"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="87"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="87"/>
-      <c r="O17" s="89"/>
-      <c r="P17" s="41" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="41" t="s">
-        <v>363</v>
-      </c>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="59"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="56"/>
+      <c r="U17" s="41"/>
     </row>
     <row r="18" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A18" s="43" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B18" s="44">
         <v>32005</v>
       </c>
       <c r="C18" s="45">
-        <v>24469</v>
+        <v>25535</v>
       </c>
       <c r="D18" s="45">
-        <v>25267</v>
+        <v>26134</v>
       </c>
       <c r="E18" s="46">
-        <v>-0.03</v>
+        <f>C18/D18-1</f>
+        <v>-2.2920333664957493E-2</v>
       </c>
       <c r="F18" s="47">
-        <v>0.76</v>
+        <f>C18/B18</f>
+        <v>0.79784408686142794</v>
       </c>
       <c r="G18" s="46">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="45">
         <v>3449</v>
       </c>
       <c r="J18" s="45">
-        <v>1590</v>
+        <v>2656</v>
       </c>
       <c r="K18" s="45">
-        <v>1292</v>
+        <v>2158</v>
       </c>
       <c r="L18" s="47">
-        <v>0.23</v>
+        <f>J18/K18-1</f>
+        <v>0.23076923076923084</v>
       </c>
       <c r="M18" s="47">
-        <v>0.46</v>
+        <f>J18/I18</f>
+        <v>0.77007828356045227</v>
       </c>
       <c r="N18" s="47">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O18" s="48"/>
       <c r="P18" s="48"/>
       <c r="Q18" s="17"/>
-      <c r="R18" s="48">
-        <v>760</v>
+      <c r="R18" s="45">
+        <v>1065</v>
       </c>
       <c r="S18" s="48">
-        <v>627</v>
+        <v>866</v>
       </c>
       <c r="T18" s="47">
-        <v>0.21</v>
+        <f>R18/S18-1</f>
+        <v>0.22979214780600454</v>
       </c>
       <c r="U18" s="48"/>
     </row>
     <row r="19" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A19" s="49" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B19" s="50">
         <v>34222</v>
       </c>
       <c r="C19" s="51">
-        <v>31397</v>
+        <v>32236</v>
       </c>
       <c r="D19" s="51">
-        <v>26085</v>
+        <v>26696</v>
       </c>
       <c r="E19" s="52">
-        <v>0.2</v>
+        <f>C19/D19-1</f>
+        <v>0.2075217261012885</v>
       </c>
       <c r="F19" s="52">
-        <v>0.92</v>
+        <f>C19/B19</f>
+        <v>0.94196715563088074</v>
       </c>
       <c r="G19" s="52">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="51">
         <v>3471</v>
       </c>
       <c r="J19" s="51">
-        <v>1794</v>
+        <v>2634</v>
       </c>
       <c r="K19" s="51">
-        <v>1450</v>
+        <v>2061</v>
       </c>
       <c r="L19" s="52">
-        <v>0.24</v>
+        <f>J19/K19-1</f>
+        <v>0.27802037845705962</v>
       </c>
       <c r="M19" s="52">
-        <v>0.52</v>
-      </c>
-      <c r="N19" s="53">
-        <v>-0.05</v>
-      </c>
-      <c r="O19" s="54"/>
-      <c r="P19" s="54"/>
+        <f>J19/I19</f>
+        <v>0.75885911840968023</v>
+      </c>
+      <c r="N19" s="92">
+        <v>0.08</v>
+      </c>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
       <c r="Q19" s="17"/>
-      <c r="R19" s="54">
-        <v>703</v>
-      </c>
-      <c r="S19" s="54">
-        <v>633</v>
+      <c r="R19" s="53">
+        <v>840</v>
+      </c>
+      <c r="S19" s="53">
+        <v>624</v>
       </c>
       <c r="T19" s="52">
-        <v>0.11</v>
-      </c>
-      <c r="U19" s="54"/>
+        <f>R19/S19-1</f>
+        <v>0.34615384615384626</v>
+      </c>
+      <c r="U19" s="53"/>
     </row>
     <row r="20" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A20" s="35" t="s">
@@ -8744,71 +8773,78 @@
         <v>108496</v>
       </c>
       <c r="C20" s="31">
-        <v>103897</v>
+        <v>106425</v>
       </c>
       <c r="D20" s="31">
-        <v>120791</v>
+        <v>122900</v>
       </c>
       <c r="E20" s="32">
-        <v>-0.14000000000000001</v>
+        <f>C20/D20-1</f>
+        <v>-0.13405207485760784</v>
       </c>
       <c r="F20" s="33">
-        <v>0.96</v>
+        <f>C20/B20</f>
+        <v>0.98091173868161041</v>
       </c>
       <c r="G20" s="32">
-        <v>-0.08</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="31">
         <v>10600</v>
       </c>
       <c r="J20" s="31">
-        <v>5854</v>
+        <v>8382</v>
       </c>
       <c r="K20" s="31">
-        <v>6378</v>
+        <v>8486</v>
       </c>
       <c r="L20" s="32">
-        <v>-0.08</v>
+        <f>J20/K20-1</f>
+        <v>-1.2255479613481057E-2</v>
       </c>
       <c r="M20" s="33">
-        <v>0.55000000000000004</v>
+        <f>J20/I20</f>
+        <v>0.79075471698113209</v>
       </c>
       <c r="N20" s="33">
-        <v>0.03</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O20" s="18"/>
       <c r="P20" s="18"/>
       <c r="Q20" s="17"/>
       <c r="R20" s="31">
-        <v>2648</v>
+        <v>2528</v>
       </c>
       <c r="S20" s="31">
-        <v>2539</v>
+        <v>2136</v>
       </c>
       <c r="T20" s="33">
-        <v>0.04</v>
+        <f>R20/S20-1</f>
+        <v>0.18352059925093633</v>
       </c>
       <c r="U20" s="18"/>
     </row>
     <row r="21" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B21" s="36">
         <v>3000</v>
       </c>
       <c r="C21" s="31">
-        <v>3160</v>
+        <v>3204</v>
       </c>
       <c r="D21" s="31">
-        <v>2925</v>
+        <v>2980</v>
       </c>
       <c r="E21" s="33">
-        <v>0.08</v>
+        <f>C21/D21-1</f>
+        <v>7.5167785234899309E-2</v>
       </c>
       <c r="F21" s="33">
-        <v>1.05</v>
+        <f>C21/B21</f>
+        <v>1.0680000000000001</v>
       </c>
       <c r="G21" s="33">
         <v>0.08</v>
@@ -8818,65 +8854,93 @@
         <v>250</v>
       </c>
       <c r="J21" s="18">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="K21" s="18">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="L21" s="32">
-        <v>-0.08</v>
+        <f>J21/K21-1</f>
+        <v>-0.10599078341013823</v>
       </c>
       <c r="M21" s="33">
-        <v>0.6</v>
+        <f>J21/I21</f>
+        <v>0.77600000000000002</v>
       </c>
       <c r="N21" s="32">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
       <c r="Q21" s="17"/>
       <c r="R21" s="18">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="S21" s="18">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="T21" s="33">
-        <v>0.62</v>
+        <f>R21/S21-1</f>
+        <v>-0.18181818181818177</v>
       </c>
       <c r="U21" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="I1:P1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="R10:U10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
     <mergeCell ref="U11:U12"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
@@ -8893,60 +8957,35 @@
     <mergeCell ref="R11:R12"/>
     <mergeCell ref="S11:S12"/>
     <mergeCell ref="T11:T12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="I10:P10"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="I1:P1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="S16:S17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backdata.xlsx
+++ b/backdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AD0883\AI\영업대쉬보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D8AD6F-EE50-4AAB-A698-29E87D77D1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECE5DBF-CC01-4490-B4D4-5C343A54F764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1098,9 +1098,6 @@
     <t>25년 누계</t>
   </si>
   <si>
-    <t>46주차</t>
-  </si>
-  <si>
     <t>목표</t>
   </si>
   <si>
@@ -1128,9 +1125,6 @@
     <t>단체비중</t>
   </si>
   <si>
-    <t>단제비중</t>
-  </si>
-  <si>
     <t>합계</t>
   </si>
   <si>
@@ -1153,6 +1147,14 @@
   </si>
   <si>
     <t>도매</t>
+  </si>
+  <si>
+    <t>47주차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단체비중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7915,7 +7917,7 @@
       <c r="P1" s="85"/>
       <c r="Q1" s="17"/>
       <c r="R1" s="85" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="S1" s="85"/>
       <c r="T1" s="85"/>
@@ -7924,60 +7926,60 @@
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="81"/>
       <c r="B2" s="86" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="D2" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="E2" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="F2" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="G2" s="18" t="s">
         <v>347</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>348</v>
       </c>
       <c r="H2" s="72"/>
       <c r="I2" s="72" t="s">
+        <v>342</v>
+      </c>
+      <c r="J2" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="J2" s="72" t="s">
+      <c r="K2" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="L2" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="L2" s="72" t="s">
+      <c r="M2" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="M2" s="72" t="s">
+      <c r="N2" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="N2" s="18" t="s">
-        <v>348</v>
-      </c>
       <c r="O2" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="P2" s="72" t="s">
         <v>350</v>
-      </c>
-      <c r="P2" s="72" t="s">
-        <v>351</v>
       </c>
       <c r="Q2" s="80"/>
       <c r="R2" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="S2" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="S2" s="72" t="s">
+      <c r="T2" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="T2" s="72" t="s">
-        <v>346</v>
-      </c>
       <c r="U2" s="72" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -7988,7 +7990,7 @@
       <c r="E3" s="73"/>
       <c r="F3" s="73"/>
       <c r="G3" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H3" s="72"/>
       <c r="I3" s="73"/>
@@ -7997,10 +7999,10 @@
       <c r="L3" s="73"/>
       <c r="M3" s="73"/>
       <c r="N3" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P3" s="73"/>
       <c r="Q3" s="80"/>
@@ -8011,7 +8013,7 @@
     </row>
     <row r="4" spans="1:21" ht="24" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B4" s="21">
         <v>315598</v>
@@ -8216,7 +8218,7 @@
     </row>
     <row r="8" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B8" s="36">
         <v>39543</v>
@@ -8299,7 +8301,7 @@
     </row>
     <row r="10" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A10" s="81" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B10" s="83" t="s">
         <v>341</v>
@@ -8322,7 +8324,7 @@
       <c r="P10" s="85"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="85" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="S10" s="85"/>
       <c r="T10" s="85"/>
@@ -8331,60 +8333,60 @@
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="81"/>
       <c r="B11" s="86" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="D11" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="E11" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="E11" s="72" t="s">
+      <c r="F11" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="G11" s="18" t="s">
         <v>347</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>348</v>
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="72" t="s">
+        <v>342</v>
+      </c>
+      <c r="J11" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="J11" s="72" t="s">
+      <c r="K11" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="K11" s="72" t="s">
+      <c r="L11" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="L11" s="72" t="s">
+      <c r="M11" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="M11" s="72" t="s">
+      <c r="N11" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="N11" s="18" t="s">
-        <v>348</v>
-      </c>
       <c r="O11" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="P11" s="72" t="s">
         <v>350</v>
-      </c>
-      <c r="P11" s="72" t="s">
-        <v>351</v>
       </c>
       <c r="Q11" s="80"/>
       <c r="R11" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="S11" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="S11" s="72" t="s">
+      <c r="T11" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="T11" s="72" t="s">
-        <v>346</v>
-      </c>
       <c r="U11" s="72" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8395,7 +8397,7 @@
       <c r="E12" s="73"/>
       <c r="F12" s="73"/>
       <c r="G12" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="73"/>
@@ -8404,10 +8406,10 @@
       <c r="L12" s="73"/>
       <c r="M12" s="73"/>
       <c r="N12" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O12" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P12" s="73"/>
       <c r="Q12" s="80"/>
@@ -8418,7 +8420,7 @@
     </row>
     <row r="13" spans="1:21" ht="24" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B13" s="21">
         <v>315598</v>
@@ -8478,7 +8480,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="74" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B14" s="75">
         <v>81716</v>
@@ -8563,7 +8565,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="67" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B16" s="68">
         <v>56159</v>
@@ -8647,7 +8649,7 @@
     </row>
     <row r="18" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A18" s="43" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B18" s="44">
         <v>32005</v>
@@ -8707,7 +8709,7 @@
     </row>
     <row r="19" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A19" s="49" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B19" s="50">
         <v>34222</v>
@@ -8827,7 +8829,7 @@
     </row>
     <row r="21" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B21" s="36">
         <v>3000</v>

--- a/backdata.xlsx
+++ b/backdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AD0883\AI\영업대쉬보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECE5DBF-CC01-4490-B4D4-5C343A54F764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D78877-D497-4759-A387-D5FC1B95ADE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="월별목표" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="상권구분" sheetId="3" r:id="rId3"/>
     <sheet name="11월실적" sheetId="4" r:id="rId4"/>
     <sheet name="주간회의" sheetId="5" r:id="rId5"/>
+    <sheet name="DC율" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="373">
   <si>
     <t>1월</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1154,6 +1155,47 @@
   </si>
   <si>
     <t>단체비중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단제비중</t>
+  </si>
+  <si>
+    <t>(전년21%)</t>
+  </si>
+  <si>
+    <t>(전년35%)</t>
+  </si>
+  <si>
+    <t>(전년28%)</t>
+  </si>
+  <si>
+    <t>(전년50%)</t>
+  </si>
+  <si>
+    <t>(전년20%)</t>
+  </si>
+  <si>
+    <t>(전년31%)</t>
+  </si>
+  <si>
+    <t>실판가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>택가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25년</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>24년</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전년 DC율</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1161,10 +1203,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1267,19 +1310,13 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1488,13 +1525,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1649,80 +1689,35 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1745,24 +1740,77 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="백분율" xfId="1" builtinId="5"/>
+    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -7893,70 +7941,70 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="66" t="s">
         <v>340</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="85" t="s">
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="85" t="s">
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="70" t="s">
         <v>359</v>
       </c>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="86" t="s">
+      <c r="S1" s="70"/>
+      <c r="T1" s="70"/>
+      <c r="U1" s="70"/>
+    </row>
+    <row r="2" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="66"/>
+      <c r="B2" s="71" t="s">
         <v>342</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="64" t="s">
         <v>344</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="64" t="s">
         <v>345</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="64" t="s">
         <v>346</v>
       </c>
       <c r="G2" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72" t="s">
+      <c r="H2" s="64"/>
+      <c r="I2" s="64" t="s">
         <v>342</v>
       </c>
-      <c r="J2" s="72" t="s">
+      <c r="J2" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="64" t="s">
         <v>344</v>
       </c>
-      <c r="L2" s="72" t="s">
+      <c r="L2" s="64" t="s">
         <v>345</v>
       </c>
-      <c r="M2" s="72" t="s">
+      <c r="M2" s="64" t="s">
         <v>346</v>
       </c>
       <c r="N2" s="18" t="s">
@@ -7965,51 +8013,51 @@
       <c r="O2" s="18" t="s">
         <v>349</v>
       </c>
-      <c r="P2" s="72" t="s">
+      <c r="P2" s="64" t="s">
         <v>350</v>
       </c>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="72" t="s">
+      <c r="Q2" s="81"/>
+      <c r="R2" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="S2" s="72" t="s">
+      <c r="S2" s="64" t="s">
         <v>344</v>
       </c>
-      <c r="T2" s="72" t="s">
+      <c r="T2" s="64" t="s">
         <v>345</v>
       </c>
-      <c r="U2" s="72" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="82"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
+      <c r="U2" s="64" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="67"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
       <c r="G3" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="H3" s="72"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
       <c r="N3" s="19" t="s">
         <v>348</v>
       </c>
       <c r="O3" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
     </row>
     <row r="4" spans="1:21" ht="24" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
@@ -8019,21 +8067,19 @@
         <v>315598</v>
       </c>
       <c r="C4" s="22">
-        <v>296877</v>
+        <v>296879</v>
       </c>
       <c r="D4" s="22">
-        <v>308397</v>
+        <v>308400</v>
       </c>
       <c r="E4" s="23">
-        <f>C4/D4-1</f>
-        <v>-3.7354448973239029E-2</v>
+        <v>-0.04</v>
       </c>
       <c r="F4" s="24">
-        <f>C4/B4</f>
-        <v>0.94068086616518487</v>
+        <v>0.94</v>
       </c>
       <c r="G4" s="23">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="25">
@@ -8043,18 +8089,16 @@
         <v>25902</v>
       </c>
       <c r="K4" s="25">
-        <v>23809</v>
+        <v>23810</v>
       </c>
       <c r="L4" s="26">
-        <f>J4/K4-1</f>
-        <v>8.7907933974547436E-2</v>
+        <v>0.09</v>
       </c>
       <c r="M4" s="26">
-        <f>J4/I4</f>
-        <v>0.78490909090909089</v>
+        <v>0.78</v>
       </c>
       <c r="N4" s="26">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="O4" s="27"/>
       <c r="P4" s="27"/>
@@ -8063,98 +8107,102 @@
         <v>7814</v>
       </c>
       <c r="S4" s="28">
-        <v>7212</v>
+        <v>7213</v>
       </c>
       <c r="T4" s="29">
-        <f>R4/S4-1</f>
-        <v>8.3471991125901202E-2</v>
+        <v>0.08</v>
       </c>
       <c r="U4" s="30"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="73" t="s">
         <v>270</v>
       </c>
       <c r="B5" s="75">
         <v>167559</v>
       </c>
-      <c r="C5" s="61">
-        <v>150845</v>
-      </c>
-      <c r="D5" s="61">
-        <v>155417</v>
-      </c>
-      <c r="E5" s="62">
-        <f>C5/D5-1</f>
-        <v>-2.9417631275857836E-2</v>
-      </c>
-      <c r="F5" s="64">
-        <f>C5/B5</f>
-        <v>0.90025006117248252</v>
-      </c>
-      <c r="G5" s="62">
-        <v>0</v>
-      </c>
-      <c r="H5" s="72"/>
-      <c r="I5" s="61">
+      <c r="C5" s="77">
+        <v>150844</v>
+      </c>
+      <c r="D5" s="77">
+        <v>155418</v>
+      </c>
+      <c r="E5" s="79">
+        <v>-0.03</v>
+      </c>
+      <c r="F5" s="82">
+        <v>0.9</v>
+      </c>
+      <c r="G5" s="79">
+        <v>-0.02</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="77">
         <v>18249</v>
       </c>
-      <c r="J5" s="61">
+      <c r="J5" s="77">
         <v>14335</v>
       </c>
-      <c r="K5" s="61">
-        <v>12988</v>
-      </c>
-      <c r="L5" s="64">
-        <f>J5/K5-1</f>
-        <v>0.1037111179550354</v>
-      </c>
-      <c r="M5" s="64">
-        <f>J5/I5</f>
-        <v>0.78552249438325383</v>
-      </c>
-      <c r="N5" s="64">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="O5" s="78"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="59">
-        <v>0.22</v>
-      </c>
-      <c r="R5" s="61">
-        <v>4457</v>
-      </c>
-      <c r="S5" s="61">
-        <v>4412</v>
-      </c>
-      <c r="T5" s="88">
-        <f>R5/S5-1</f>
-        <v>1.0199456029011733E-2</v>
-      </c>
-      <c r="U5" s="34"/>
+      <c r="K5" s="77">
+        <v>12989</v>
+      </c>
+      <c r="L5" s="82">
+        <v>0.1</v>
+      </c>
+      <c r="M5" s="82">
+        <v>0.79</v>
+      </c>
+      <c r="N5" s="82">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O5" s="84">
+        <v>-0.05</v>
+      </c>
+      <c r="P5" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="Q5" s="86">
+        <v>0.21</v>
+      </c>
+      <c r="R5" s="77">
+        <v>4456</v>
+      </c>
+      <c r="S5" s="77">
+        <v>4413</v>
+      </c>
+      <c r="T5" s="82">
+        <v>0.01</v>
+      </c>
+      <c r="U5" s="34">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="67"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="89"/>
-      <c r="U6" s="16"/>
+      <c r="A6" s="74"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q6" s="86"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78"/>
+      <c r="T6" s="83"/>
+      <c r="U6" s="16" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="7" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
@@ -8164,21 +8212,19 @@
         <v>108496</v>
       </c>
       <c r="C7" s="31">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D7" s="31">
-        <v>122900</v>
+        <v>122902</v>
       </c>
       <c r="E7" s="32">
-        <f>C7/D7-1</f>
-        <v>-0.13405207485760784</v>
+        <v>-0.13</v>
       </c>
       <c r="F7" s="33">
-        <f>C7/B7</f>
-        <v>0.98091173868161041</v>
+        <v>0.98</v>
       </c>
       <c r="G7" s="32">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="H7" s="18"/>
       <c r="I7" s="31">
@@ -8188,18 +8234,16 @@
         <v>8382</v>
       </c>
       <c r="K7" s="31">
-        <v>8486</v>
+        <v>8487</v>
       </c>
       <c r="L7" s="32">
-        <f>J7/K7-1</f>
-        <v>-1.2255479613481057E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="M7" s="33">
-        <f>J7/I7</f>
-        <v>0.79075471698113209</v>
+        <v>0.79</v>
       </c>
       <c r="N7" s="33">
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="O7" s="18"/>
       <c r="P7" s="18"/>
@@ -8211,8 +8255,7 @@
         <v>2136</v>
       </c>
       <c r="T7" s="33">
-        <f>R7/S7-1</f>
-        <v>0.18352059925093633</v>
+        <v>0.18</v>
       </c>
       <c r="U7" s="17"/>
     </row>
@@ -8227,52 +8270,47 @@
         <v>39607</v>
       </c>
       <c r="D8" s="31">
-        <v>30079</v>
+        <v>30080</v>
       </c>
       <c r="E8" s="33">
-        <f>C8/D8-1</f>
-        <v>0.31676584992852153</v>
+        <v>0.32</v>
       </c>
       <c r="F8" s="33">
-        <f>C8/B8</f>
-        <v>1.001618491262676</v>
+        <v>1</v>
       </c>
       <c r="G8" s="33">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H8" s="18"/>
       <c r="I8" s="31">
         <v>4151</v>
       </c>
       <c r="J8" s="31">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="K8" s="31">
         <v>2334</v>
       </c>
       <c r="L8" s="33">
-        <f>J8/K8-1</f>
-        <v>0.36418166238217653</v>
+        <v>0.36</v>
       </c>
       <c r="M8" s="33">
-        <f>J8/I8</f>
-        <v>0.76704408576246685</v>
+        <v>0.77</v>
       </c>
       <c r="N8" s="33">
-        <v>0.12</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O8" s="18"/>
       <c r="P8" s="18"/>
       <c r="Q8" s="17"/>
       <c r="R8" s="18">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="S8" s="18">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="T8" s="33">
-        <f>R8/S8-1</f>
-        <v>0.24886877828054299</v>
+        <v>0.25</v>
       </c>
       <c r="U8" s="17"/>
     </row>
@@ -8300,70 +8338,70 @@
       <c r="U9" s="17"/>
     </row>
     <row r="10" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="68" t="s">
         <v>341</v>
       </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
       <c r="H10" s="16"/>
-      <c r="I10" s="85" t="s">
+      <c r="I10" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="85"/>
-      <c r="K10" s="85"/>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="85"/>
-      <c r="O10" s="85"/>
-      <c r="P10" s="85"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
       <c r="Q10" s="17"/>
-      <c r="R10" s="85" t="s">
+      <c r="R10" s="70" t="s">
         <v>359</v>
       </c>
-      <c r="S10" s="85"/>
-      <c r="T10" s="85"/>
-      <c r="U10" s="85"/>
+      <c r="S10" s="70"/>
+      <c r="T10" s="70"/>
+      <c r="U10" s="70"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="81"/>
-      <c r="B11" s="86" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="71" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="64" t="s">
         <v>344</v>
       </c>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="64" t="s">
         <v>345</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="64" t="s">
         <v>346</v>
       </c>
       <c r="G11" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="H11" s="71"/>
-      <c r="I11" s="72" t="s">
+      <c r="H11" s="87"/>
+      <c r="I11" s="64" t="s">
         <v>342</v>
       </c>
-      <c r="J11" s="72" t="s">
+      <c r="J11" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="K11" s="72" t="s">
+      <c r="K11" s="64" t="s">
         <v>344</v>
       </c>
-      <c r="L11" s="72" t="s">
+      <c r="L11" s="64" t="s">
         <v>345</v>
       </c>
-      <c r="M11" s="72" t="s">
+      <c r="M11" s="64" t="s">
         <v>346</v>
       </c>
       <c r="N11" s="18" t="s">
@@ -8372,51 +8410,51 @@
       <c r="O11" s="18" t="s">
         <v>349</v>
       </c>
-      <c r="P11" s="72" t="s">
+      <c r="P11" s="64" t="s">
         <v>350</v>
       </c>
-      <c r="Q11" s="80"/>
-      <c r="R11" s="72" t="s">
+      <c r="Q11" s="81"/>
+      <c r="R11" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="S11" s="72" t="s">
+      <c r="S11" s="64" t="s">
         <v>344</v>
       </c>
-      <c r="T11" s="72" t="s">
+      <c r="T11" s="64" t="s">
         <v>345</v>
       </c>
-      <c r="U11" s="72" t="s">
+      <c r="U11" s="64" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="82"/>
-      <c r="B12" s="87"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
       <c r="G12" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="H12" s="71"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="73"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
       <c r="N12" s="19" t="s">
         <v>348</v>
       </c>
       <c r="O12" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="P12" s="73"/>
-      <c r="Q12" s="80"/>
-      <c r="R12" s="73"/>
-      <c r="S12" s="73"/>
-      <c r="T12" s="73"/>
-      <c r="U12" s="73"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="65"/>
+      <c r="U12" s="65"/>
     </row>
     <row r="13" spans="1:21" ht="24" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
@@ -8479,173 +8517,184 @@
       <c r="U13" s="30"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="73" t="s">
         <v>354</v>
       </c>
       <c r="B14" s="75">
         <v>81716</v>
       </c>
-      <c r="C14" s="61">
+      <c r="C14" s="77">
         <v>76086</v>
       </c>
-      <c r="D14" s="61">
-        <v>77288</v>
-      </c>
-      <c r="E14" s="76">
-        <f>C14/D14-1</f>
-        <v>-1.5552220267053052E-2</v>
-      </c>
-      <c r="F14" s="64">
-        <f>C14/B14</f>
-        <v>0.93110284399627985</v>
-      </c>
-      <c r="G14" s="90">
-        <v>0.01</v>
-      </c>
-      <c r="H14" s="71"/>
-      <c r="I14" s="61">
+      <c r="D14" s="77">
+        <v>77289</v>
+      </c>
+      <c r="E14" s="88">
+        <v>-0.02</v>
+      </c>
+      <c r="F14" s="82">
+        <v>0.93</v>
+      </c>
+      <c r="G14" s="84">
+        <v>-0.01</v>
+      </c>
+      <c r="H14" s="87"/>
+      <c r="I14" s="77">
         <v>8970</v>
       </c>
-      <c r="J14" s="61">
+      <c r="J14" s="77">
         <v>6904</v>
       </c>
-      <c r="K14" s="61">
+      <c r="K14" s="77">
         <v>6540</v>
       </c>
-      <c r="L14" s="64">
-        <f>J14/K14-1</f>
-        <v>5.5657492354740157E-2</v>
-      </c>
-      <c r="M14" s="70">
-        <f>J14/I14</f>
-        <v>0.7696767001114827</v>
-      </c>
-      <c r="N14" s="64">
+      <c r="L14" s="82">
+        <v>0.06</v>
+      </c>
+      <c r="M14" s="90">
+        <v>0.77</v>
+      </c>
+      <c r="N14" s="82">
+        <v>0.03</v>
+      </c>
+      <c r="O14" s="93">
+        <v>-0.15</v>
+      </c>
+      <c r="P14" s="42">
+        <v>0.42</v>
+      </c>
+      <c r="Q14" s="86">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R14" s="77">
+        <v>1999</v>
+      </c>
+      <c r="S14" s="77">
+        <v>2007</v>
+      </c>
+      <c r="T14" s="79">
+        <v>0</v>
+      </c>
+      <c r="U14" s="42">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="74"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="83"/>
+      <c r="O15" s="94"/>
+      <c r="P15" s="41" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q15" s="86"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="41" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="74" t="s">
+        <v>355</v>
+      </c>
+      <c r="B16" s="76">
+        <v>56159</v>
+      </c>
+      <c r="C16" s="78">
+        <v>53389</v>
+      </c>
+      <c r="D16" s="78">
+        <v>52396</v>
+      </c>
+      <c r="E16" s="92">
+        <v>0.02</v>
+      </c>
+      <c r="F16" s="83">
+        <v>0.95</v>
+      </c>
+      <c r="G16" s="91">
+        <v>0.04</v>
+      </c>
+      <c r="H16" s="87"/>
+      <c r="I16" s="78">
+        <v>6260</v>
+      </c>
+      <c r="J16" s="78">
+        <v>5131</v>
+      </c>
+      <c r="K16" s="78">
+        <v>4345</v>
+      </c>
+      <c r="L16" s="83">
+        <v>0.18</v>
+      </c>
+      <c r="M16" s="91">
+        <v>0.82</v>
+      </c>
+      <c r="N16" s="83">
         <v>0.11</v>
       </c>
-      <c r="O14" s="65"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="59">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="R14" s="61">
-        <v>1998</v>
-      </c>
-      <c r="S14" s="61">
-        <v>2007</v>
-      </c>
-      <c r="T14" s="62">
-        <f>R14/S14-1</f>
-        <v>-4.484304932735439E-3</v>
-      </c>
-      <c r="U14" s="42"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="67"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="57"/>
-      <c r="N15" s="56"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="59"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="63"/>
-      <c r="U15" s="41"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="67" t="s">
-        <v>355</v>
-      </c>
-      <c r="B16" s="68">
-        <v>56159</v>
-      </c>
-      <c r="C16" s="60">
-        <v>50485</v>
-      </c>
-      <c r="D16" s="60">
-        <v>49355</v>
-      </c>
-      <c r="E16" s="69">
-        <v>0.02</v>
-      </c>
-      <c r="F16" s="56">
-        <f>C16/D16-1</f>
-        <v>2.2895350015196048E-2</v>
-      </c>
-      <c r="G16" s="57">
-        <v>0.06</v>
-      </c>
-      <c r="H16" s="71"/>
-      <c r="I16" s="60">
-        <v>6260</v>
-      </c>
-      <c r="J16" s="60">
-        <v>4892</v>
-      </c>
-      <c r="K16" s="60">
-        <v>4179</v>
-      </c>
-      <c r="L16" s="56">
-        <f>J16/K16-1</f>
-        <v>0.17061497966020589</v>
-      </c>
-      <c r="M16" s="57">
-        <f>J16/I16</f>
-        <v>0.78146964856230028</v>
-      </c>
-      <c r="N16" s="56">
-        <v>0.17</v>
-      </c>
-      <c r="O16" s="58"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="59">
+      <c r="O16" s="94">
+        <v>-0.01</v>
+      </c>
+      <c r="P16" s="40">
+        <v>0.33</v>
+      </c>
+      <c r="Q16" s="86">
         <v>0.2</v>
       </c>
-      <c r="R16" s="60">
-        <v>1273</v>
-      </c>
-      <c r="S16" s="60">
-        <v>1479</v>
-      </c>
-      <c r="T16" s="56">
-        <f>R16/S16-1</f>
-        <v>-0.13928329952670726</v>
-      </c>
-      <c r="U16" s="40"/>
+      <c r="R16" s="78">
+        <v>1336</v>
+      </c>
+      <c r="S16" s="78">
+        <v>1522</v>
+      </c>
+      <c r="T16" s="80">
+        <v>-0.12</v>
+      </c>
+      <c r="U16" s="40">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="67"/>
-      <c r="B17" s="68"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="56"/>
-      <c r="M17" s="57"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="59"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="56"/>
-      <c r="U17" s="41"/>
+      <c r="A17" s="74"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="83"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="83"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q17" s="86"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="78"/>
+      <c r="T17" s="80"/>
+      <c r="U17" s="41" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="18" spans="1:21" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A18" s="43" t="s">
@@ -8655,21 +8704,19 @@
         <v>32005</v>
       </c>
       <c r="C18" s="45">
-        <v>25535</v>
+        <v>25534</v>
       </c>
       <c r="D18" s="45">
-        <v>26134</v>
+        <v>26135</v>
       </c>
       <c r="E18" s="46">
-        <f>C18/D18-1</f>
-        <v>-2.2920333664957493E-2</v>
+        <v>-0.02</v>
       </c>
       <c r="F18" s="47">
-        <f>C18/B18</f>
-        <v>0.79784408686142794</v>
+        <v>0.8</v>
       </c>
       <c r="G18" s="46">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="45">
@@ -8679,18 +8726,16 @@
         <v>2656</v>
       </c>
       <c r="K18" s="45">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="L18" s="47">
-        <f>J18/K18-1</f>
-        <v>0.23076923076923084</v>
+        <v>0.23</v>
       </c>
       <c r="M18" s="47">
-        <f>J18/I18</f>
-        <v>0.77007828356045227</v>
+        <v>0.77</v>
       </c>
       <c r="N18" s="47">
-        <v>0.2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O18" s="48"/>
       <c r="P18" s="48"/>
@@ -8699,11 +8744,10 @@
         <v>1065</v>
       </c>
       <c r="S18" s="48">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="T18" s="47">
-        <f>R18/S18-1</f>
-        <v>0.22979214780600454</v>
+        <v>0.23</v>
       </c>
       <c r="U18" s="48"/>
     </row>
@@ -8715,18 +8759,16 @@
         <v>34222</v>
       </c>
       <c r="C19" s="51">
-        <v>32236</v>
+        <v>32237</v>
       </c>
       <c r="D19" s="51">
-        <v>26696</v>
+        <v>26697</v>
       </c>
       <c r="E19" s="52">
-        <f>C19/D19-1</f>
-        <v>0.2075217261012885</v>
+        <v>0.21</v>
       </c>
       <c r="F19" s="52">
-        <f>C19/B19</f>
-        <v>0.94196715563088074</v>
+        <v>0.94</v>
       </c>
       <c r="G19" s="52">
         <v>0.06</v>
@@ -8739,18 +8781,16 @@
         <v>2634</v>
       </c>
       <c r="K19" s="51">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="L19" s="52">
-        <f>J19/K19-1</f>
-        <v>0.27802037845705962</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M19" s="52">
-        <f>J19/I19</f>
-        <v>0.75885911840968023</v>
-      </c>
-      <c r="N19" s="92">
-        <v>0.08</v>
+        <v>0.76</v>
+      </c>
+      <c r="N19" s="52">
+        <v>0.02</v>
       </c>
       <c r="O19" s="53"/>
       <c r="P19" s="53"/>
@@ -8759,11 +8799,10 @@
         <v>840</v>
       </c>
       <c r="S19" s="53">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="T19" s="52">
-        <f>R19/S19-1</f>
-        <v>0.34615384615384626</v>
+        <v>0.35</v>
       </c>
       <c r="U19" s="53"/>
     </row>
@@ -8781,15 +8820,13 @@
         <v>122900</v>
       </c>
       <c r="E20" s="32">
-        <f>C20/D20-1</f>
-        <v>-0.13405207485760784</v>
+        <v>-0.13</v>
       </c>
       <c r="F20" s="33">
-        <f>C20/B20</f>
-        <v>0.98091173868161041</v>
+        <v>0.98</v>
       </c>
       <c r="G20" s="32">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="31">
@@ -8799,18 +8836,16 @@
         <v>8382</v>
       </c>
       <c r="K20" s="31">
-        <v>8486</v>
+        <v>8487</v>
       </c>
       <c r="L20" s="32">
-        <f>J20/K20-1</f>
-        <v>-1.2255479613481057E-2</v>
+        <v>-0.01</v>
       </c>
       <c r="M20" s="33">
-        <f>J20/I20</f>
-        <v>0.79075471698113209</v>
+        <v>0.79</v>
       </c>
       <c r="N20" s="33">
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="O20" s="18"/>
       <c r="P20" s="18"/>
@@ -8822,8 +8857,7 @@
         <v>2136</v>
       </c>
       <c r="T20" s="33">
-        <f>R20/S20-1</f>
-        <v>0.18352059925093633</v>
+        <v>0.18</v>
       </c>
       <c r="U20" s="18"/>
     </row>
@@ -8835,18 +8869,16 @@
         <v>3000</v>
       </c>
       <c r="C21" s="31">
-        <v>3204</v>
+        <v>3205</v>
       </c>
       <c r="D21" s="31">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="E21" s="33">
-        <f>C21/D21-1</f>
-        <v>7.5167785234899309E-2</v>
+        <v>0.08</v>
       </c>
       <c r="F21" s="33">
-        <f>C21/B21</f>
-        <v>1.0680000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="G21" s="33">
         <v>0.08</v>
@@ -8862,12 +8894,10 @@
         <v>217</v>
       </c>
       <c r="L21" s="32">
-        <f>J21/K21-1</f>
-        <v>-0.10599078341013823</v>
+        <v>-0.11</v>
       </c>
       <c r="M21" s="33">
-        <f>J21/I21</f>
-        <v>0.77600000000000002</v>
+        <v>0.78</v>
       </c>
       <c r="N21" s="32">
         <v>-0.11</v>
@@ -8879,16 +8909,98 @@
         <v>45</v>
       </c>
       <c r="S21" s="18">
-        <v>55</v>
-      </c>
-      <c r="T21" s="33">
-        <f>R21/S21-1</f>
-        <v>-0.18181818181818177</v>
+        <v>56</v>
+      </c>
+      <c r="T21" s="32">
+        <v>-0.19</v>
       </c>
       <c r="U21" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="99">
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="R10:U10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:G1"/>
@@ -8905,91 +9017,4842 @@
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="I10:P10"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="S16:S17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB8680F-0643-4DAC-AE41-629A933465DA}">
+  <dimension ref="A3:I215"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="57" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>369</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="61">
+        <v>1984394500</v>
+      </c>
+      <c r="C10" s="57">
+        <v>1991099500</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1652590100</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1655444000</v>
+      </c>
+      <c r="G10" s="95">
+        <f>(F10-E10)/F10</f>
+        <v>1.7239483788035112E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="61">
+        <v>1732741700</v>
+      </c>
+      <c r="C11" s="57">
+        <v>1736480000</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1625162900</v>
+      </c>
+      <c r="F11" s="11">
+        <v>1626118100</v>
+      </c>
+      <c r="G11" s="95">
+        <f t="shared" ref="G11:G74" si="0">(F11-E11)/F11</f>
+        <v>5.8741120955482882E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="61">
+        <v>1570519800</v>
+      </c>
+      <c r="C12" s="57">
+        <v>1605504400</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1108453600</v>
+      </c>
+      <c r="F12" s="11">
+        <v>1121842900</v>
+      </c>
+      <c r="G12" s="95">
+        <f t="shared" si="0"/>
+        <v>1.1935093585741819E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="61">
+        <v>1101852700</v>
+      </c>
+      <c r="C13" s="57">
+        <v>1102567600</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1078607400</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1108932000</v>
+      </c>
+      <c r="G13" s="95">
+        <f t="shared" si="0"/>
+        <v>2.7345770525153933E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="61">
+        <v>1040337200</v>
+      </c>
+      <c r="C14" s="57">
+        <v>1040858300</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="14">
+        <v>924552000</v>
+      </c>
+      <c r="F14" s="11">
+        <v>926780400</v>
+      </c>
+      <c r="G14" s="95">
+        <f t="shared" si="0"/>
+        <v>2.4044530937425953E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="61">
+        <v>448845600</v>
+      </c>
+      <c r="C15" s="57">
+        <v>532734100</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="14">
+        <v>876409500</v>
+      </c>
+      <c r="F15" s="11">
+        <v>906449700</v>
+      </c>
+      <c r="G15" s="95">
+        <f t="shared" si="0"/>
+        <v>3.3140504100779115E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="61">
+        <v>357955300</v>
+      </c>
+      <c r="C16" s="57">
+        <v>359179900</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="14">
+        <v>524902600</v>
+      </c>
+      <c r="F16" s="11">
+        <v>525227800</v>
+      </c>
+      <c r="G16" s="95">
+        <f t="shared" si="0"/>
+        <v>6.1915991499307543E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="61">
+        <v>355560300</v>
+      </c>
+      <c r="C17" s="57">
+        <v>370302300</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="14">
+        <v>415539800</v>
+      </c>
+      <c r="F17" s="11">
+        <v>420942300</v>
+      </c>
+      <c r="G17" s="95">
+        <f t="shared" si="0"/>
+        <v>1.2834300568035096E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="61">
+        <v>308152200</v>
+      </c>
+      <c r="C18" s="57">
+        <v>308360700</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="14">
+        <v>355509200</v>
+      </c>
+      <c r="F18" s="11">
+        <v>415817000</v>
+      </c>
+      <c r="G18" s="95">
+        <f t="shared" si="0"/>
+        <v>0.14503447429999256</v>
+      </c>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" s="61">
+        <v>296687400</v>
+      </c>
+      <c r="C19" s="57">
+        <v>312257700</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" s="14">
+        <v>331423710</v>
+      </c>
+      <c r="F19" s="11">
+        <v>355551900</v>
+      </c>
+      <c r="G19" s="95">
+        <f t="shared" si="0"/>
+        <v>6.7861232073292255E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="61">
+        <v>286103100</v>
+      </c>
+      <c r="C20" s="57">
+        <v>286617000</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="14">
+        <v>280612000</v>
+      </c>
+      <c r="F20" s="11">
+        <v>281803000</v>
+      </c>
+      <c r="G20" s="95">
+        <f t="shared" si="0"/>
+        <v>4.2263567101840649E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B21" s="61">
+        <v>273197500</v>
+      </c>
+      <c r="C21" s="57">
+        <v>289316500</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="14">
+        <v>258007410</v>
+      </c>
+      <c r="F21" s="11">
+        <v>261105900</v>
+      </c>
+      <c r="G21" s="95">
+        <f t="shared" si="0"/>
+        <v>1.1866794277724095E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" s="61">
+        <v>262558200</v>
+      </c>
+      <c r="C22" s="57">
+        <v>284577800</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E22" s="14">
+        <v>213586100</v>
+      </c>
+      <c r="F22" s="11">
+        <v>226829600</v>
+      </c>
+      <c r="G22" s="95">
+        <f t="shared" si="0"/>
+        <v>5.8385237200083234E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="61">
+        <v>237079400</v>
+      </c>
+      <c r="C23" s="57">
+        <v>248914700</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E23" s="14">
+        <v>208342530</v>
+      </c>
+      <c r="F23" s="11">
+        <v>220828700</v>
+      </c>
+      <c r="G23" s="95">
+        <f t="shared" si="0"/>
+        <v>5.6542333491978174E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B24" s="61">
+        <v>235404500</v>
+      </c>
+      <c r="C24" s="57">
+        <v>242005100</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E24" s="14">
+        <v>178433110</v>
+      </c>
+      <c r="F24" s="11">
+        <v>182042500</v>
+      </c>
+      <c r="G24" s="95">
+        <f t="shared" si="0"/>
+        <v>1.9827183212711319E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="61">
+        <v>222622600</v>
+      </c>
+      <c r="C25" s="57">
+        <v>243131200</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="E25" s="14">
+        <v>174170410</v>
+      </c>
+      <c r="F25" s="11">
+        <v>189059900</v>
+      </c>
+      <c r="G25" s="95">
+        <f t="shared" si="0"/>
+        <v>7.8755410322336988E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" s="61">
+        <v>155323500</v>
+      </c>
+      <c r="C26" s="57">
+        <v>168791400</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="14">
+        <v>166545500</v>
+      </c>
+      <c r="F26" s="11">
+        <v>172375800</v>
+      </c>
+      <c r="G26" s="95">
+        <f t="shared" si="0"/>
+        <v>3.3823193278870935E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27" s="61">
+        <v>152035300</v>
+      </c>
+      <c r="C27" s="57">
+        <v>156627200</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="14">
+        <v>159790530</v>
+      </c>
+      <c r="F27" s="11">
+        <v>180530300</v>
+      </c>
+      <c r="G27" s="95">
+        <f t="shared" si="0"/>
+        <v>0.1148824878704572</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="61">
+        <v>148792500</v>
+      </c>
+      <c r="C28" s="57">
+        <v>156492100</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28" s="14">
+        <v>153988000</v>
+      </c>
+      <c r="F28" s="11">
+        <v>160928000</v>
+      </c>
+      <c r="G28" s="95">
+        <f t="shared" si="0"/>
+        <v>4.3124875720819252E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="61">
+        <v>146984300</v>
+      </c>
+      <c r="C29" s="57">
+        <v>155528900</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E29" s="14">
+        <v>145752300</v>
+      </c>
+      <c r="F29" s="11">
+        <v>156963900</v>
+      </c>
+      <c r="G29" s="95">
+        <f t="shared" si="0"/>
+        <v>7.1427888833037412E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="61">
+        <v>136280000</v>
+      </c>
+      <c r="C30" s="57">
+        <v>148500000</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" s="14">
+        <v>143596400</v>
+      </c>
+      <c r="F30" s="11">
+        <v>148644000</v>
+      </c>
+      <c r="G30" s="95">
+        <f t="shared" si="0"/>
+        <v>3.3957643766314147E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B31" s="61">
+        <v>134451500</v>
+      </c>
+      <c r="C31" s="57">
+        <v>144684700</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E31" s="14">
+        <v>142907000</v>
+      </c>
+      <c r="F31" s="11">
+        <v>149080000</v>
+      </c>
+      <c r="G31" s="95">
+        <f t="shared" si="0"/>
+        <v>4.1407298094982559E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="61">
+        <v>134203400</v>
+      </c>
+      <c r="C32" s="57">
+        <v>141657100</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="14">
+        <v>139680300</v>
+      </c>
+      <c r="F32" s="11">
+        <v>151115800</v>
+      </c>
+      <c r="G32" s="95">
+        <f t="shared" si="0"/>
+        <v>7.5673754829078094E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" s="61">
+        <v>133348100</v>
+      </c>
+      <c r="C33" s="57">
+        <v>137497600</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="14">
+        <v>138842700</v>
+      </c>
+      <c r="F33" s="11">
+        <v>145219000</v>
+      </c>
+      <c r="G33" s="95">
+        <f t="shared" si="0"/>
+        <v>4.3908166286780653E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="61">
+        <v>131659700</v>
+      </c>
+      <c r="C34" s="57">
+        <v>142944800</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E34" s="14">
+        <v>129476300</v>
+      </c>
+      <c r="F34" s="11">
+        <v>139260000</v>
+      </c>
+      <c r="G34" s="95">
+        <f t="shared" si="0"/>
+        <v>7.0254918856814591E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" s="61">
+        <v>130709600</v>
+      </c>
+      <c r="C35" s="57">
+        <v>136626400</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E35" s="14">
+        <v>121181600</v>
+      </c>
+      <c r="F35" s="11">
+        <v>128520900</v>
+      </c>
+      <c r="G35" s="95">
+        <f t="shared" si="0"/>
+        <v>5.7105887058058261E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="61">
+        <v>124908300</v>
+      </c>
+      <c r="C36" s="57">
+        <v>133473800</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" s="14">
+        <v>114319420</v>
+      </c>
+      <c r="F36" s="11">
+        <v>117719400</v>
+      </c>
+      <c r="G36" s="95">
+        <f t="shared" si="0"/>
+        <v>2.8882070414901876E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B37" s="61">
+        <v>123731300</v>
+      </c>
+      <c r="C37" s="57">
+        <v>130190300</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E37" s="14">
+        <v>112715900</v>
+      </c>
+      <c r="F37" s="11">
+        <v>117911600</v>
+      </c>
+      <c r="G37" s="95">
+        <f t="shared" si="0"/>
+        <v>4.4064366864668109E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" s="61">
+        <v>123590500</v>
+      </c>
+      <c r="C38" s="57">
+        <v>128649600</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="14">
+        <v>110644200</v>
+      </c>
+      <c r="F38" s="11">
+        <v>119682900</v>
+      </c>
+      <c r="G38" s="95">
+        <f t="shared" si="0"/>
+        <v>7.5522067062211901E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39" s="61">
+        <v>121782700</v>
+      </c>
+      <c r="C39" s="57">
+        <v>133507700</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E39" s="14">
+        <v>109311300</v>
+      </c>
+      <c r="F39" s="11">
+        <v>114865500</v>
+      </c>
+      <c r="G39" s="95">
+        <f t="shared" si="0"/>
+        <v>4.8353944395836873E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="61">
+        <v>113045400</v>
+      </c>
+      <c r="C40" s="57">
+        <v>121845800</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="14">
+        <v>107774400</v>
+      </c>
+      <c r="F40" s="11">
+        <v>115684900</v>
+      </c>
+      <c r="G40" s="95">
+        <f t="shared" si="0"/>
+        <v>6.8379710748766698E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="61">
+        <v>109498700</v>
+      </c>
+      <c r="C41" s="57">
+        <v>114592500</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E41" s="14">
+        <v>100608500</v>
+      </c>
+      <c r="F41" s="11">
+        <v>105888900</v>
+      </c>
+      <c r="G41" s="95">
+        <f t="shared" si="0"/>
+        <v>4.9867360979290558E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B42" s="61">
+        <v>108779100</v>
+      </c>
+      <c r="C42" s="57">
+        <v>114210100</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E42" s="14">
+        <v>97257200</v>
+      </c>
+      <c r="F42" s="11">
+        <v>103300000</v>
+      </c>
+      <c r="G42" s="95">
+        <f t="shared" si="0"/>
+        <v>5.8497579864472411E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="61">
+        <v>99520400</v>
+      </c>
+      <c r="C43" s="57">
+        <v>103735200</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="14">
+        <v>92545710</v>
+      </c>
+      <c r="F43" s="11">
+        <v>94417900</v>
+      </c>
+      <c r="G43" s="95">
+        <f t="shared" si="0"/>
+        <v>1.9828761283612537E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="61">
+        <v>93312200</v>
+      </c>
+      <c r="C44" s="57">
+        <v>100813200</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="14">
+        <v>88585300</v>
+      </c>
+      <c r="F44" s="11">
+        <v>93481900</v>
+      </c>
+      <c r="G44" s="95">
+        <f t="shared" si="0"/>
+        <v>5.2380193385029618E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" s="61">
+        <v>87281100</v>
+      </c>
+      <c r="C45" s="57">
+        <v>94185800</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="14">
+        <v>82869500</v>
+      </c>
+      <c r="F45" s="11">
+        <v>96703000</v>
+      </c>
+      <c r="G45" s="95">
+        <f t="shared" si="0"/>
+        <v>0.14305140481681022</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" s="61">
+        <v>84776200</v>
+      </c>
+      <c r="C46" s="57">
+        <v>90206700</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="E46" s="14">
+        <v>80966900</v>
+      </c>
+      <c r="F46" s="11">
+        <v>85844000</v>
+      </c>
+      <c r="G46" s="95">
+        <f t="shared" si="0"/>
+        <v>5.6813522203066028E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" s="61">
+        <v>83230200</v>
+      </c>
+      <c r="C47" s="57">
+        <v>94048400</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="14">
+        <v>79618000</v>
+      </c>
+      <c r="F47" s="11">
+        <v>82007900</v>
+      </c>
+      <c r="G47" s="95">
+        <f t="shared" si="0"/>
+        <v>2.9142314338008898E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" s="61">
+        <v>81096000</v>
+      </c>
+      <c r="C48" s="57">
+        <v>84815900</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E48" s="14">
+        <v>79327500</v>
+      </c>
+      <c r="F48" s="11">
+        <v>82776000</v>
+      </c>
+      <c r="G48" s="95">
+        <f t="shared" si="0"/>
+        <v>4.1660626268483616E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" s="61">
+        <v>78313100</v>
+      </c>
+      <c r="C49" s="57">
+        <v>84885300</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E49" s="14">
+        <v>78963700</v>
+      </c>
+      <c r="F49" s="11">
+        <v>82472000</v>
+      </c>
+      <c r="G49" s="95">
+        <f t="shared" si="0"/>
+        <v>4.2539286060723637E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" s="61">
+        <v>77719100</v>
+      </c>
+      <c r="C50" s="57">
+        <v>81172800</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E50" s="14">
+        <v>77497000</v>
+      </c>
+      <c r="F50" s="11">
+        <v>86304500</v>
+      </c>
+      <c r="G50" s="95">
+        <f t="shared" si="0"/>
+        <v>0.10205145733999965</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="61">
+        <v>75535400</v>
+      </c>
+      <c r="C51" s="57">
+        <v>83365000</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E51" s="14">
+        <v>77313730</v>
+      </c>
+      <c r="F51" s="11">
+        <v>80759600</v>
+      </c>
+      <c r="G51" s="95">
+        <f t="shared" si="0"/>
+        <v>4.266824006062437E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="61">
+        <v>73245900</v>
+      </c>
+      <c r="C52" s="57">
+        <v>77021500</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" s="14">
+        <v>74084800</v>
+      </c>
+      <c r="F52" s="11">
+        <v>80454900</v>
+      </c>
+      <c r="G52" s="95">
+        <f t="shared" si="0"/>
+        <v>7.9176035269449094E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="61">
+        <v>69488200</v>
+      </c>
+      <c r="C53" s="57">
+        <v>71259200</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E53" s="14">
+        <v>73984500</v>
+      </c>
+      <c r="F53" s="11">
+        <v>76408900</v>
+      </c>
+      <c r="G53" s="95">
+        <f t="shared" si="0"/>
+        <v>3.1729288080315249E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="61">
+        <v>64876200</v>
+      </c>
+      <c r="C54" s="57">
+        <v>68257100</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="E54" s="14">
+        <v>73333800</v>
+      </c>
+      <c r="F54" s="11">
+        <v>77793000</v>
+      </c>
+      <c r="G54" s="95">
+        <f t="shared" si="0"/>
+        <v>5.7321352820947899E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="61">
+        <v>63531200</v>
+      </c>
+      <c r="C55" s="57">
+        <v>68024300</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="E55" s="14">
+        <v>71958700</v>
+      </c>
+      <c r="F55" s="11">
+        <v>73821000</v>
+      </c>
+      <c r="G55" s="95">
+        <f t="shared" si="0"/>
+        <v>2.5227238861570557E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B56" s="61">
+        <v>63481300</v>
+      </c>
+      <c r="C56" s="57">
+        <v>68849500</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E56" s="14">
+        <v>69918800</v>
+      </c>
+      <c r="F56" s="11">
+        <v>72498000</v>
+      </c>
+      <c r="G56" s="95">
+        <f t="shared" si="0"/>
+        <v>3.55761538249331E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B57" s="61">
+        <v>62926900</v>
+      </c>
+      <c r="C57" s="57">
+        <v>66739300</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E57" s="14">
+        <v>68610800</v>
+      </c>
+      <c r="F57" s="11">
+        <v>78860000</v>
+      </c>
+      <c r="G57" s="95">
+        <f t="shared" si="0"/>
+        <v>0.12996703018006595</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B58" s="61">
+        <v>60603800</v>
+      </c>
+      <c r="C58" s="57">
+        <v>63776300</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E58" s="14">
+        <v>67662300</v>
+      </c>
+      <c r="F58" s="11">
+        <v>71304000</v>
+      </c>
+      <c r="G58" s="95">
+        <f t="shared" si="0"/>
+        <v>5.1072871087176036E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" s="61">
+        <v>60405600</v>
+      </c>
+      <c r="C59" s="57">
+        <v>61500600</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="E59" s="14">
+        <v>67440800</v>
+      </c>
+      <c r="F59" s="11">
+        <v>73089000</v>
+      </c>
+      <c r="G59" s="95">
+        <f t="shared" si="0"/>
+        <v>7.7278386624526269E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B60" s="61">
+        <v>59433800</v>
+      </c>
+      <c r="C60" s="57">
+        <v>63162500</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E60" s="14">
+        <v>65484800</v>
+      </c>
+      <c r="F60" s="11">
+        <v>67505000</v>
+      </c>
+      <c r="G60" s="95">
+        <f t="shared" si="0"/>
+        <v>2.9926672098363083E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" s="61">
+        <v>58715800</v>
+      </c>
+      <c r="C61" s="57">
+        <v>61882800</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E61" s="14">
+        <v>65115600</v>
+      </c>
+      <c r="F61" s="11">
+        <v>69337000</v>
+      </c>
+      <c r="G61" s="95">
+        <f t="shared" si="0"/>
+        <v>6.0882357183033586E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B62" s="61">
+        <v>58293600</v>
+      </c>
+      <c r="C62" s="57">
+        <v>69870800</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E62" s="14">
+        <v>63193900</v>
+      </c>
+      <c r="F62" s="11">
+        <v>69256900</v>
+      </c>
+      <c r="G62" s="95">
+        <f t="shared" si="0"/>
+        <v>8.7543623812212215E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B63" s="61">
+        <v>58030000</v>
+      </c>
+      <c r="C63" s="57">
+        <v>60574700</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E63" s="14">
+        <v>59040890</v>
+      </c>
+      <c r="F63" s="11">
+        <v>70038800</v>
+      </c>
+      <c r="G63" s="95">
+        <f t="shared" si="0"/>
+        <v>0.15702596275207456</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B64" s="61">
+        <v>57084000</v>
+      </c>
+      <c r="C64" s="57">
+        <v>61811800</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E64" s="14">
+        <v>56570500</v>
+      </c>
+      <c r="F64" s="11">
+        <v>60262000</v>
+      </c>
+      <c r="G64" s="95">
+        <f t="shared" si="0"/>
+        <v>6.1257508877899838E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B65" s="61">
+        <v>55912400</v>
+      </c>
+      <c r="C65" s="57">
+        <v>60501500</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E65" s="14">
+        <v>53838600</v>
+      </c>
+      <c r="F65" s="11">
+        <v>56045000</v>
+      </c>
+      <c r="G65" s="95">
+        <f t="shared" si="0"/>
+        <v>3.9368364706931933E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="61">
+        <v>53866600</v>
+      </c>
+      <c r="C66" s="57">
+        <v>56806600</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E66" s="14">
+        <v>52666300</v>
+      </c>
+      <c r="F66" s="11">
+        <v>56309000</v>
+      </c>
+      <c r="G66" s="95">
+        <f t="shared" si="0"/>
+        <v>6.4691257170256977E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" s="61">
+        <v>51137910</v>
+      </c>
+      <c r="C67" s="57">
+        <v>55099000</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E67" s="14">
+        <v>51003200</v>
+      </c>
+      <c r="F67" s="11">
+        <v>53663000</v>
+      </c>
+      <c r="G67" s="95">
+        <f t="shared" si="0"/>
+        <v>4.9564877103404584E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B68" s="61">
+        <v>50538200</v>
+      </c>
+      <c r="C68" s="57">
+        <v>52601000</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E68" s="14">
+        <v>50044400</v>
+      </c>
+      <c r="F68" s="11">
+        <v>51879000</v>
+      </c>
+      <c r="G68" s="95">
+        <f t="shared" si="0"/>
+        <v>3.5363056342643459E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" s="61">
+        <v>50317210</v>
+      </c>
+      <c r="C69" s="57">
+        <v>55401000</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E69" s="14">
+        <v>48784400</v>
+      </c>
+      <c r="F69" s="11">
+        <v>49765000</v>
+      </c>
+      <c r="G69" s="95">
+        <f t="shared" si="0"/>
+        <v>1.9704611674871898E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B70" s="61">
+        <v>47971530</v>
+      </c>
+      <c r="C70" s="57">
+        <v>51906400</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E70" s="14">
+        <v>46494200</v>
+      </c>
+      <c r="F70" s="11">
+        <v>48400500</v>
+      </c>
+      <c r="G70" s="95">
+        <f t="shared" si="0"/>
+        <v>3.9385956756645073E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B71" s="61">
+        <v>46861200</v>
+      </c>
+      <c r="C71" s="57">
+        <v>50140700</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E71" s="14">
+        <v>46390110</v>
+      </c>
+      <c r="F71" s="11">
+        <v>51579900</v>
+      </c>
+      <c r="G71" s="95">
+        <f t="shared" si="0"/>
+        <v>0.10061651922551226</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" s="61">
+        <v>44998020</v>
+      </c>
+      <c r="C72" s="57">
+        <v>51258700</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" s="14">
+        <v>46075500</v>
+      </c>
+      <c r="F72" s="11">
+        <v>47600000</v>
+      </c>
+      <c r="G72" s="95">
+        <f t="shared" si="0"/>
+        <v>3.2027310924369751E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B73" s="61">
+        <v>44754500</v>
+      </c>
+      <c r="C73" s="57">
+        <v>46990400</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="14">
+        <v>43962100</v>
+      </c>
+      <c r="F73" s="11">
+        <v>48378000</v>
+      </c>
+      <c r="G73" s="95">
+        <f t="shared" si="0"/>
+        <v>9.1279093802968295E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B74" s="61">
+        <v>43999700</v>
+      </c>
+      <c r="C74" s="57">
+        <v>46846500</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E74" s="14">
+        <v>43539300</v>
+      </c>
+      <c r="F74" s="11">
+        <v>46185000</v>
+      </c>
+      <c r="G74" s="95">
+        <f t="shared" si="0"/>
+        <v>5.7284832737901914E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" s="61">
+        <v>43031310</v>
+      </c>
+      <c r="C75" s="57">
+        <v>48477300</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="E75" s="14">
+        <v>43533000</v>
+      </c>
+      <c r="F75" s="11">
+        <v>46529000</v>
+      </c>
+      <c r="G75" s="95">
+        <f t="shared" ref="G75:G138" si="1">(F75-E75)/F75</f>
+        <v>6.4389950353542946E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B76" s="61">
+        <v>41441600</v>
+      </c>
+      <c r="C76" s="57">
+        <v>43571900</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E76" s="14">
+        <v>43159700</v>
+      </c>
+      <c r="F76" s="11">
+        <v>50844900</v>
+      </c>
+      <c r="G76" s="95">
+        <f t="shared" si="1"/>
+        <v>0.15114986950510279</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B77" s="61">
+        <v>37927100</v>
+      </c>
+      <c r="C77" s="57">
+        <v>39877100</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E77" s="14">
+        <v>42019700</v>
+      </c>
+      <c r="F77" s="11">
+        <v>44070000</v>
+      </c>
+      <c r="G77" s="95">
+        <f t="shared" si="1"/>
+        <v>4.6523712275924667E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B78" s="61">
+        <v>32418700</v>
+      </c>
+      <c r="C78" s="57">
+        <v>34252800</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E78" s="14">
+        <v>41597700</v>
+      </c>
+      <c r="F78" s="11">
+        <v>44114800</v>
+      </c>
+      <c r="G78" s="95">
+        <f t="shared" si="1"/>
+        <v>5.7057948806296298E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" s="61">
+        <v>31784000</v>
+      </c>
+      <c r="C79" s="57">
+        <v>33883900</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E79" s="14">
+        <v>41319500</v>
+      </c>
+      <c r="F79" s="11">
+        <v>43192000</v>
+      </c>
+      <c r="G79" s="95">
+        <f t="shared" si="1"/>
+        <v>4.3352935728838672E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B80" s="61">
+        <v>28790300</v>
+      </c>
+      <c r="C80" s="57">
+        <v>30561400</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E80" s="14">
+        <v>41214300</v>
+      </c>
+      <c r="F80" s="11">
+        <v>42597000</v>
+      </c>
+      <c r="G80" s="95">
+        <f t="shared" si="1"/>
+        <v>3.2460032396647652E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B81" s="61">
+        <v>26575500</v>
+      </c>
+      <c r="C81" s="57">
+        <v>27633400</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="14">
+        <v>40479800</v>
+      </c>
+      <c r="F81" s="11">
+        <v>42182000</v>
+      </c>
+      <c r="G81" s="95">
+        <f t="shared" si="1"/>
+        <v>4.0353705371959606E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B82" s="61">
+        <v>25182100</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E82" s="14">
+        <v>38743300</v>
+      </c>
+      <c r="F82" s="11">
+        <v>38906000</v>
+      </c>
+      <c r="G82" s="95">
+        <f t="shared" si="1"/>
+        <v>4.1818742610394283E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="61">
+        <v>14955000</v>
+      </c>
+      <c r="C83" s="57">
+        <v>15945700</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E83" s="14">
+        <v>38429700</v>
+      </c>
+      <c r="F83" s="11">
+        <v>39928000</v>
+      </c>
+      <c r="G83" s="95">
+        <f t="shared" si="1"/>
+        <v>3.7525045081146062E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="62"/>
+      <c r="B84" s="62"/>
+      <c r="C84" s="63">
+        <v>15801440800</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E84" s="14">
+        <v>37808000</v>
+      </c>
+      <c r="F84" s="11">
+        <v>41567000</v>
+      </c>
+      <c r="G84" s="95">
+        <f t="shared" si="1"/>
+        <v>9.0432314095315991E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B85" s="61">
+        <v>895978600</v>
+      </c>
+      <c r="C85" s="57">
+        <v>904448500</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E85" s="14">
+        <v>36650800</v>
+      </c>
+      <c r="F85" s="11">
+        <v>41506900</v>
+      </c>
+      <c r="G85" s="95">
+        <f t="shared" si="1"/>
+        <v>0.11699500564966307</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B86" s="61">
+        <v>891329300</v>
+      </c>
+      <c r="C86" s="57">
+        <v>893585200</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="E86" s="14">
+        <v>33428300</v>
+      </c>
+      <c r="F86" s="11">
+        <v>37307000</v>
+      </c>
+      <c r="G86" s="95">
+        <f t="shared" si="1"/>
+        <v>0.10396708392526871</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B87" s="61">
+        <v>830496450</v>
+      </c>
+      <c r="C87" s="57">
+        <v>931135600</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E87" s="14">
+        <v>30818100</v>
+      </c>
+      <c r="F87" s="11">
+        <v>33111900</v>
+      </c>
+      <c r="G87" s="95">
+        <f t="shared" si="1"/>
+        <v>6.927418843376551E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B88" s="61">
+        <v>562297500</v>
+      </c>
+      <c r="C88" s="57">
+        <v>583976500</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E88" s="14">
+        <v>20180000</v>
+      </c>
+      <c r="F88" s="11">
+        <v>22312000</v>
+      </c>
+      <c r="G88" s="95">
+        <f t="shared" si="1"/>
+        <v>9.5553961993546072E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B89" s="61">
+        <v>331413800</v>
+      </c>
+      <c r="C89" s="57">
+        <v>341949200</v>
+      </c>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12">
+        <v>15555834800</v>
+      </c>
+      <c r="G89" s="95">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B90" s="61">
+        <v>194204430</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="E90" s="14">
+        <v>757366500</v>
+      </c>
+      <c r="F90" s="11">
+        <v>772889300</v>
+      </c>
+      <c r="G90" s="95">
+        <f t="shared" si="1"/>
+        <v>2.0084118126619168E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B91" s="61">
+        <v>193567300</v>
+      </c>
+      <c r="C91" s="57">
+        <v>243574700</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="E91" s="14">
+        <v>643541830</v>
+      </c>
+      <c r="F91" s="11">
+        <v>714948500</v>
+      </c>
+      <c r="G91" s="95">
+        <f t="shared" si="1"/>
+        <v>9.9876662444917358E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B92" s="61">
+        <v>154325200</v>
+      </c>
+      <c r="C92" s="57">
+        <v>164232400</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E92" s="14">
+        <v>582372900</v>
+      </c>
+      <c r="G92" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B93" s="61">
+        <v>132278700</v>
+      </c>
+      <c r="C93" s="57">
+        <v>133089300</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="E93" s="14">
+        <v>430060500</v>
+      </c>
+      <c r="G93" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B94" s="61">
+        <v>131116400</v>
+      </c>
+      <c r="C94" s="57">
+        <v>137572700</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="E94" s="14">
+        <v>320886000</v>
+      </c>
+      <c r="F94" s="11">
+        <v>422177800</v>
+      </c>
+      <c r="G94" s="95">
+        <f t="shared" si="1"/>
+        <v>0.23992687441168153</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B95" s="61">
+        <v>111773000</v>
+      </c>
+      <c r="C95" s="57">
+        <v>113484000</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E95" s="14">
+        <v>217153566</v>
+      </c>
+      <c r="G95" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B96" s="61">
+        <v>111499800</v>
+      </c>
+      <c r="C96" s="57">
+        <v>111707700</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="E96" s="14">
+        <v>161576700</v>
+      </c>
+      <c r="G96" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B97" s="61">
+        <v>104228200</v>
+      </c>
+      <c r="C97" s="57">
+        <v>106238000</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E97" s="14">
+        <v>121380400</v>
+      </c>
+      <c r="F97" s="11">
+        <v>134936800</v>
+      </c>
+      <c r="G97" s="95">
+        <f t="shared" si="1"/>
+        <v>0.10046481019262352</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B98" s="61">
+        <v>102807100</v>
+      </c>
+      <c r="C98" s="57">
+        <v>121741800</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="E98" s="14">
+        <v>101611184</v>
+      </c>
+      <c r="F98" s="11">
+        <v>113147900</v>
+      </c>
+      <c r="G98" s="95">
+        <f t="shared" si="1"/>
+        <v>0.1019613797516348</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B99" s="61">
+        <v>99045000</v>
+      </c>
+      <c r="C99" s="57">
+        <v>102742500</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E99" s="14">
+        <v>92641400</v>
+      </c>
+      <c r="G99" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B100" s="61">
+        <v>91196300</v>
+      </c>
+      <c r="C100" s="57">
+        <v>94828200</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="E100" s="14">
+        <v>90379210</v>
+      </c>
+      <c r="F100" s="11">
+        <v>92973900</v>
+      </c>
+      <c r="G100" s="95">
+        <f t="shared" si="1"/>
+        <v>2.79077246410014E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B101" s="61">
+        <v>90912700</v>
+      </c>
+      <c r="C101" s="57">
+        <v>93695300</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="E101" s="14">
+        <v>89336900</v>
+      </c>
+      <c r="F101" s="11">
+        <v>89382000</v>
+      </c>
+      <c r="G101" s="95">
+        <f t="shared" si="1"/>
+        <v>5.0457586538676686E-4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B102" s="61">
+        <v>87549400</v>
+      </c>
+      <c r="C102" s="57">
+        <v>88985700</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="E102" s="14">
+        <v>85622800</v>
+      </c>
+      <c r="F102" s="11">
+        <v>89780000</v>
+      </c>
+      <c r="G102" s="95">
+        <f t="shared" si="1"/>
+        <v>4.6304299398529737E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B103" s="61">
+        <v>77158100</v>
+      </c>
+      <c r="C103" s="57">
+        <v>80269500</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="E103" s="14">
+        <v>83505800</v>
+      </c>
+      <c r="F103" s="11">
+        <v>91335900</v>
+      </c>
+      <c r="G103" s="95">
+        <f t="shared" si="1"/>
+        <v>8.572861273606544E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B104" s="61">
+        <v>56463300</v>
+      </c>
+      <c r="C104" s="57">
+        <v>58089500</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="E104" s="14">
+        <v>73633100</v>
+      </c>
+      <c r="F104" s="11">
+        <v>73992900</v>
+      </c>
+      <c r="G104" s="95">
+        <f t="shared" si="1"/>
+        <v>4.8626287116736878E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B105" s="61">
+        <v>54227200</v>
+      </c>
+      <c r="C105" s="57">
+        <v>58670800</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="E105" s="14">
+        <v>68250900</v>
+      </c>
+      <c r="G105" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B106" s="61">
+        <v>50367000</v>
+      </c>
+      <c r="C106" s="57">
+        <v>53466200</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="E106" s="14">
+        <v>63143900</v>
+      </c>
+      <c r="F106" s="11">
+        <v>67220000</v>
+      </c>
+      <c r="G106" s="95">
+        <f t="shared" si="1"/>
+        <v>6.0638202915798869E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B107" s="61">
+        <v>47489300</v>
+      </c>
+      <c r="C107" s="57">
+        <v>51660300</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E107" s="14">
+        <v>63012900</v>
+      </c>
+      <c r="G107" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B108" s="61">
+        <v>33395400</v>
+      </c>
+      <c r="C108" s="57">
+        <v>34875400</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E108" s="14">
+        <v>61374600</v>
+      </c>
+      <c r="G108" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B109" s="61">
+        <v>30735500</v>
+      </c>
+      <c r="C109" s="57">
+        <v>34786700</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E109" s="14">
+        <v>60494800</v>
+      </c>
+      <c r="F109" s="11">
+        <v>60920000</v>
+      </c>
+      <c r="G109" s="95">
+        <f t="shared" si="1"/>
+        <v>6.9796454366382139E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B110" s="61">
+        <v>13334800</v>
+      </c>
+      <c r="C110" s="57">
+        <v>13866400</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="E110" s="14">
+        <v>57519400</v>
+      </c>
+      <c r="F110" s="11">
+        <v>62278800</v>
+      </c>
+      <c r="G110" s="95">
+        <f t="shared" si="1"/>
+        <v>7.6420868738639791E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B111" s="61">
+        <v>6865244</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="E111" s="14">
+        <v>56041601</v>
+      </c>
+      <c r="F111" s="11">
+        <v>58013600</v>
+      </c>
+      <c r="G111" s="95">
+        <f t="shared" si="1"/>
+        <v>3.3992012217824788E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="62"/>
+      <c r="B112" s="62"/>
+      <c r="C112" s="63">
+        <v>5552672100</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E112" s="14">
+        <v>42939900</v>
+      </c>
+      <c r="F112" s="11">
+        <v>44954800</v>
+      </c>
+      <c r="G112" s="95">
+        <f t="shared" si="1"/>
+        <v>4.4820575333446036E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B113" s="61">
+        <v>424392796</v>
+      </c>
+      <c r="C113" s="57">
+        <v>448470700</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E113" s="14">
+        <v>36872200</v>
+      </c>
+      <c r="G113" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B114" s="61">
+        <v>329085549</v>
+      </c>
+      <c r="C114" s="57">
+        <v>349209300</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="E114" s="14">
+        <v>29479600</v>
+      </c>
+      <c r="F114" s="11">
+        <v>30228700</v>
+      </c>
+      <c r="G114" s="95">
+        <f t="shared" si="1"/>
+        <v>2.4781085524683496E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B115" s="61">
+        <v>243593752</v>
+      </c>
+      <c r="C115" s="57">
+        <v>256755300</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="E115" s="14">
+        <v>28369000</v>
+      </c>
+      <c r="F115" s="11">
+        <v>31013900</v>
+      </c>
+      <c r="G115" s="95">
+        <f t="shared" si="1"/>
+        <v>8.5281115886747555E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B116" s="61">
+        <v>242265100</v>
+      </c>
+      <c r="C116" s="57">
+        <v>256821500</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E116" s="14">
+        <v>13550400</v>
+      </c>
+      <c r="G116" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B117" s="61">
+        <v>228068700</v>
+      </c>
+      <c r="C117" s="57">
+        <v>269038200</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E117" s="14">
+        <v>5726069</v>
+      </c>
+      <c r="G117" s="95" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B118" s="61">
+        <v>212239300</v>
+      </c>
+      <c r="C118" s="57">
+        <v>222746200</v>
+      </c>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12">
+        <v>2950194800</v>
+      </c>
+      <c r="G118" s="95">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B119" s="61">
+        <v>155988400</v>
+      </c>
+      <c r="C119" s="57">
+        <v>164047400</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E119" s="14">
+        <v>167833644</v>
+      </c>
+      <c r="F119" s="11">
+        <v>176346000</v>
+      </c>
+      <c r="G119" s="95">
+        <f t="shared" si="1"/>
+        <v>4.8270763158790107E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B120" s="61">
+        <v>133763728</v>
+      </c>
+      <c r="C120" s="57">
+        <v>142350000</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E120" s="14">
+        <v>159862800</v>
+      </c>
+      <c r="F120" s="11">
+        <v>170404000</v>
+      </c>
+      <c r="G120" s="95">
+        <f t="shared" si="1"/>
+        <v>6.1860050233562593E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B121" s="61">
+        <v>127626407</v>
+      </c>
+      <c r="C121" s="57">
+        <v>140106600</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E121" s="14">
+        <v>154052528</v>
+      </c>
+      <c r="F121" s="11">
+        <v>162081900</v>
+      </c>
+      <c r="G121" s="95">
+        <f t="shared" si="1"/>
+        <v>4.9538979984810147E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B122" s="61">
+        <v>110939929</v>
+      </c>
+      <c r="C122" s="57">
+        <v>115156600</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="E122" s="14">
+        <v>152491500</v>
+      </c>
+      <c r="F122" s="11">
+        <v>161978000</v>
+      </c>
+      <c r="G122" s="95">
+        <f t="shared" si="1"/>
+        <v>5.8566595463581471E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B123" s="61">
+        <v>99736900</v>
+      </c>
+      <c r="C123" s="57">
+        <v>109822100</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E123" s="14">
+        <v>135630700</v>
+      </c>
+      <c r="F123" s="11">
+        <v>164212000</v>
+      </c>
+      <c r="G123" s="95">
+        <f t="shared" si="1"/>
+        <v>0.17405122646335225</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B124" s="61">
+        <v>98702395</v>
+      </c>
+      <c r="C124" s="57">
+        <v>102673600</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E124" s="14">
+        <v>125674600</v>
+      </c>
+      <c r="F124" s="11">
+        <v>139743900</v>
+      </c>
+      <c r="G124" s="95">
+        <f t="shared" si="1"/>
+        <v>0.10067917096918005</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B125" s="61">
+        <v>91302473</v>
+      </c>
+      <c r="C125" s="57">
+        <v>95728600</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E125" s="14">
+        <v>106033846</v>
+      </c>
+      <c r="F125" s="11">
+        <v>107833700</v>
+      </c>
+      <c r="G125" s="95">
+        <f t="shared" si="1"/>
+        <v>1.6691015888354012E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" s="61">
+        <v>82700100</v>
+      </c>
+      <c r="C126" s="57">
+        <v>89025500</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E126" s="14">
+        <v>103868105</v>
+      </c>
+      <c r="F126" s="11">
+        <v>106825000</v>
+      </c>
+      <c r="G126" s="95">
+        <f t="shared" si="1"/>
+        <v>2.7679803416803182E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B127" s="61">
+        <v>81717398</v>
+      </c>
+      <c r="C127" s="57">
+        <v>87466200</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E127" s="14">
+        <v>99989434</v>
+      </c>
+      <c r="F127" s="11">
+        <v>100556000</v>
+      </c>
+      <c r="G127" s="95">
+        <f t="shared" si="1"/>
+        <v>5.6343331079199647E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B128" s="61">
+        <v>80681940</v>
+      </c>
+      <c r="C128" s="57">
+        <v>92167600</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E128" s="14">
+        <v>94327024</v>
+      </c>
+      <c r="F128" s="11">
+        <v>96065700</v>
+      </c>
+      <c r="G128" s="95">
+        <f t="shared" si="1"/>
+        <v>1.8098821952059894E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B129" s="61">
+        <v>76232285</v>
+      </c>
+      <c r="C129" s="57">
+        <v>79961500</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E129" s="14">
+        <v>92416032</v>
+      </c>
+      <c r="F129" s="11">
+        <v>94666800</v>
+      </c>
+      <c r="G129" s="95">
+        <f t="shared" si="1"/>
+        <v>2.3775684822979124E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B130" s="61">
+        <v>75008194</v>
+      </c>
+      <c r="C130" s="57">
+        <v>77919400</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E130" s="14">
+        <v>91798419</v>
+      </c>
+      <c r="F130" s="11">
+        <v>98974000</v>
+      </c>
+      <c r="G130" s="95">
+        <f t="shared" si="1"/>
+        <v>7.249965647543799E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B131" s="61">
+        <v>73711608</v>
+      </c>
+      <c r="C131" s="57">
+        <v>75081200</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E131" s="14">
+        <v>89403300</v>
+      </c>
+      <c r="F131" s="11">
+        <v>93167000</v>
+      </c>
+      <c r="G131" s="95">
+        <f t="shared" si="1"/>
+        <v>4.0397350993377483E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B132" s="61">
+        <v>70715610</v>
+      </c>
+      <c r="C132" s="57">
+        <v>72357400</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E132" s="14">
+        <v>88434391</v>
+      </c>
+      <c r="F132" s="11">
+        <v>92432500</v>
+      </c>
+      <c r="G132" s="95">
+        <f t="shared" si="1"/>
+        <v>4.3254363995347954E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B133" s="61">
+        <v>69062307</v>
+      </c>
+      <c r="C133" s="57">
+        <v>73213700</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E133" s="14">
+        <v>86658571</v>
+      </c>
+      <c r="F133" s="11">
+        <v>90240900</v>
+      </c>
+      <c r="G133" s="95">
+        <f t="shared" si="1"/>
+        <v>3.9697398851296917E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B134" s="61">
+        <v>64776427</v>
+      </c>
+      <c r="C134" s="57">
+        <v>69007700</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E134" s="14">
+        <v>82817000</v>
+      </c>
+      <c r="F134" s="11">
+        <v>85939900</v>
+      </c>
+      <c r="G134" s="95">
+        <f t="shared" si="1"/>
+        <v>3.633818517359224E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B135" s="61">
+        <v>64530010</v>
+      </c>
+      <c r="C135" s="57">
+        <v>70988500</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E135" s="14">
+        <v>81087556</v>
+      </c>
+      <c r="F135" s="11">
+        <v>89172800</v>
+      </c>
+      <c r="G135" s="95">
+        <f t="shared" si="1"/>
+        <v>9.0669396946153988E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B136" s="61">
+        <v>62602300</v>
+      </c>
+      <c r="C136" s="57">
+        <v>67233700</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E136" s="14">
+        <v>78213253</v>
+      </c>
+      <c r="F136" s="11">
+        <v>85358900</v>
+      </c>
+      <c r="G136" s="95">
+        <f t="shared" si="1"/>
+        <v>8.3712969590751515E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B137" s="61">
+        <v>61631300</v>
+      </c>
+      <c r="C137" s="57">
+        <v>65379500</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E137" s="14">
+        <v>77072750</v>
+      </c>
+      <c r="F137" s="11">
+        <v>81192000</v>
+      </c>
+      <c r="G137" s="95">
+        <f t="shared" si="1"/>
+        <v>5.0734678293427926E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B138" s="61">
+        <v>61056000</v>
+      </c>
+      <c r="C138" s="57">
+        <v>64048800</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E138" s="14">
+        <v>74858975</v>
+      </c>
+      <c r="F138" s="11">
+        <v>77102900</v>
+      </c>
+      <c r="G138" s="95">
+        <f t="shared" si="1"/>
+        <v>2.910299093808404E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B139" s="61">
+        <v>60967987</v>
+      </c>
+      <c r="C139" s="57">
+        <v>64946400</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E139" s="14">
+        <v>71287845</v>
+      </c>
+      <c r="F139" s="11">
+        <v>76090000</v>
+      </c>
+      <c r="G139" s="95">
+        <f t="shared" ref="G139:G202" si="2">(F139-E139)/F139</f>
+        <v>6.3111512682349852E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B140" s="61">
+        <v>59599888</v>
+      </c>
+      <c r="C140" s="57">
+        <v>62922800</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E140" s="14">
+        <v>69063293</v>
+      </c>
+      <c r="F140" s="11">
+        <v>71806000</v>
+      </c>
+      <c r="G140" s="95">
+        <f t="shared" si="2"/>
+        <v>3.8196069966298082E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B141" s="61">
+        <v>59469787</v>
+      </c>
+      <c r="C141" s="57">
+        <v>64618000</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="E141" s="14">
+        <v>67160600</v>
+      </c>
+      <c r="F141" s="11">
+        <v>75591000</v>
+      </c>
+      <c r="G141" s="95">
+        <f t="shared" si="2"/>
+        <v>0.11152650447804632</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B142" s="61">
+        <v>59227200</v>
+      </c>
+      <c r="C142" s="57">
+        <v>63167800</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E142" s="14">
+        <v>66079039</v>
+      </c>
+      <c r="F142" s="11">
+        <v>68946000</v>
+      </c>
+      <c r="G142" s="95">
+        <f t="shared" si="2"/>
+        <v>4.1582702404780555E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B143" s="61">
+        <v>58816856</v>
+      </c>
+      <c r="C143" s="57">
+        <v>61981000</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E143" s="14">
+        <v>65130900</v>
+      </c>
+      <c r="F143" s="11">
+        <v>69973000</v>
+      </c>
+      <c r="G143" s="95">
+        <f t="shared" si="2"/>
+        <v>6.9199548397238936E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B144" s="61">
+        <v>57506910</v>
+      </c>
+      <c r="C144" s="57">
+        <v>61333300</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E144" s="14">
+        <v>63838860</v>
+      </c>
+      <c r="F144" s="11">
+        <v>68528900</v>
+      </c>
+      <c r="G144" s="95">
+        <f t="shared" si="2"/>
+        <v>6.8438863019835428E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B145" s="61">
+        <v>57468900</v>
+      </c>
+      <c r="C145" s="57">
+        <v>61513700</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E145" s="14">
+        <v>63221410</v>
+      </c>
+      <c r="F145" s="11">
+        <v>69483800</v>
+      </c>
+      <c r="G145" s="95">
+        <f t="shared" si="2"/>
+        <v>9.012733903442241E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B146" s="61">
+        <v>56866978</v>
+      </c>
+      <c r="C146" s="57">
+        <v>62349000</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E146" s="14">
+        <v>62235704</v>
+      </c>
+      <c r="F146" s="11">
+        <v>65221900</v>
+      </c>
+      <c r="G146" s="95">
+        <f t="shared" si="2"/>
+        <v>4.5785173385013318E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B147" s="61">
+        <v>56288231</v>
+      </c>
+      <c r="C147" s="57">
+        <v>61600100</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E147" s="14">
+        <v>58431869</v>
+      </c>
+      <c r="F147" s="11">
+        <v>59693000</v>
+      </c>
+      <c r="G147" s="95">
+        <f t="shared" si="2"/>
+        <v>2.1126949558574706E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B148" s="61">
+        <v>51671055</v>
+      </c>
+      <c r="C148" s="57">
+        <v>54888700</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E148" s="14">
+        <v>57509861</v>
+      </c>
+      <c r="F148" s="11">
+        <v>59644000</v>
+      </c>
+      <c r="G148" s="95">
+        <f t="shared" si="2"/>
+        <v>3.5781285628059822E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B149" s="61">
+        <v>50886561</v>
+      </c>
+      <c r="C149" s="57">
+        <v>54416200</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E149" s="14">
+        <v>57486787</v>
+      </c>
+      <c r="F149" s="11">
+        <v>59301800</v>
+      </c>
+      <c r="G149" s="95">
+        <f t="shared" si="2"/>
+        <v>3.0606372825108176E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B150" s="61">
+        <v>48997100</v>
+      </c>
+      <c r="C150" s="57">
+        <v>52549400</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E150" s="14">
+        <v>55090300</v>
+      </c>
+      <c r="F150" s="11">
+        <v>55844000</v>
+      </c>
+      <c r="G150" s="95">
+        <f t="shared" si="2"/>
+        <v>1.3496526036816846E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B151" s="61">
+        <v>46553700</v>
+      </c>
+      <c r="C151" s="57">
+        <v>49380500</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E151" s="14">
+        <v>54772376</v>
+      </c>
+      <c r="F151" s="11">
+        <v>59154000</v>
+      </c>
+      <c r="G151" s="95">
+        <f t="shared" si="2"/>
+        <v>7.4071474456503361E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B152" s="61">
+        <v>45211800</v>
+      </c>
+      <c r="C152" s="57">
+        <v>48174900</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E152" s="14">
+        <v>54081300</v>
+      </c>
+      <c r="F152" s="11">
+        <v>58795000</v>
+      </c>
+      <c r="G152" s="95">
+        <f t="shared" si="2"/>
+        <v>8.0171783314907735E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B153" s="61">
+        <v>43726302</v>
+      </c>
+      <c r="C153" s="57">
+        <v>46603200</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E153" s="14">
+        <v>53832200</v>
+      </c>
+      <c r="F153" s="11">
+        <v>58970900</v>
+      </c>
+      <c r="G153" s="95">
+        <f t="shared" si="2"/>
+        <v>8.7139589187209279E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B154" s="61">
+        <v>42328300</v>
+      </c>
+      <c r="C154" s="57">
+        <v>43654800</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E154" s="14">
+        <v>53696704</v>
+      </c>
+      <c r="F154" s="11">
+        <v>58517000</v>
+      </c>
+      <c r="G154" s="95">
+        <f t="shared" si="2"/>
+        <v>8.2374284395987485E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B155" s="61">
+        <v>42020646</v>
+      </c>
+      <c r="C155" s="57">
+        <v>44620500</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E155" s="14">
+        <v>53383642</v>
+      </c>
+      <c r="F155" s="11">
+        <v>54984900</v>
+      </c>
+      <c r="G155" s="95">
+        <f t="shared" si="2"/>
+        <v>2.9121777069704591E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B156" s="61">
+        <v>41926200</v>
+      </c>
+      <c r="C156" s="57">
+        <v>44606200</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E156" s="14">
+        <v>53188405</v>
+      </c>
+      <c r="F156" s="11">
+        <v>56051900</v>
+      </c>
+      <c r="G156" s="95">
+        <f t="shared" si="2"/>
+        <v>5.1086493053759105E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B157" s="61">
+        <v>41305176</v>
+      </c>
+      <c r="C157" s="57">
+        <v>42426500</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E157" s="14">
+        <v>52567000</v>
+      </c>
+      <c r="F157" s="11">
+        <v>53203000</v>
+      </c>
+      <c r="G157" s="95">
+        <f t="shared" si="2"/>
+        <v>1.1954213108283367E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B158" s="61">
+        <v>38831668</v>
+      </c>
+      <c r="C158" s="57">
+        <v>42447300</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E158" s="14">
+        <v>49360162</v>
+      </c>
+      <c r="F158" s="11">
+        <v>52572900</v>
+      </c>
+      <c r="G158" s="95">
+        <f t="shared" si="2"/>
+        <v>6.1110153710371692E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B159" s="61">
+        <v>34960900</v>
+      </c>
+      <c r="C159" s="57">
+        <v>36728200</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E159" s="14">
+        <v>49313168</v>
+      </c>
+      <c r="F159" s="11">
+        <v>51028000</v>
+      </c>
+      <c r="G159" s="95">
+        <f t="shared" si="2"/>
+        <v>3.3605706670847377E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B160" s="61">
+        <v>34949700</v>
+      </c>
+      <c r="C160" s="57">
+        <v>36740400</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E160" s="14">
+        <v>49209256</v>
+      </c>
+      <c r="F160" s="11">
+        <v>54625700</v>
+      </c>
+      <c r="G160" s="95">
+        <f t="shared" si="2"/>
+        <v>9.9155598921386826E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B161" s="61">
+        <v>34460200</v>
+      </c>
+      <c r="C161" s="57">
+        <v>38416600</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E161" s="14">
+        <v>48511300</v>
+      </c>
+      <c r="F161" s="11">
+        <v>51568000</v>
+      </c>
+      <c r="G161" s="95">
+        <f t="shared" si="2"/>
+        <v>5.9275131864722309E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B162" s="61">
+        <v>32416019</v>
+      </c>
+      <c r="C162" s="57">
+        <v>33804600</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E162" s="14">
+        <v>44618910</v>
+      </c>
+      <c r="F162" s="11">
+        <v>49186800</v>
+      </c>
+      <c r="G162" s="95">
+        <f t="shared" si="2"/>
+        <v>9.2868208543755645E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B163" s="61">
+        <v>32089700</v>
+      </c>
+      <c r="C163" s="57">
+        <v>32730600</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E163" s="14">
+        <v>43165426</v>
+      </c>
+      <c r="F163" s="11">
+        <v>45807000</v>
+      </c>
+      <c r="G163" s="95">
+        <f t="shared" si="2"/>
+        <v>5.7667474403475451E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B164" s="61">
+        <v>31825296</v>
+      </c>
+      <c r="C164" s="57">
+        <v>34400000</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E164" s="14">
+        <v>38067200</v>
+      </c>
+      <c r="F164" s="11">
+        <v>39135900</v>
+      </c>
+      <c r="G164" s="95">
+        <f t="shared" si="2"/>
+        <v>2.7307408287531396E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B165" s="61">
+        <v>31518847</v>
+      </c>
+      <c r="C165" s="57">
+        <v>33653600</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E165" s="14">
+        <v>37233400</v>
+      </c>
+      <c r="F165" s="11">
+        <v>37533000</v>
+      </c>
+      <c r="G165" s="95">
+        <f t="shared" si="2"/>
+        <v>7.982308901500014E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B166" s="61">
+        <v>28975695</v>
+      </c>
+      <c r="C166" s="57">
+        <v>30214400</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E166" s="14">
+        <v>36909800</v>
+      </c>
+      <c r="F166" s="11">
+        <v>38384700</v>
+      </c>
+      <c r="G166" s="95">
+        <f t="shared" si="2"/>
+        <v>3.8424163794428506E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B167" s="61">
+        <v>27715700</v>
+      </c>
+      <c r="C167" s="57">
+        <v>29209200</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E167" s="14">
+        <v>34525400</v>
+      </c>
+      <c r="F167" s="11">
+        <v>35025000</v>
+      </c>
+      <c r="G167" s="95">
+        <f t="shared" si="2"/>
+        <v>1.4264097073518915E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B168" s="61">
+        <v>26717000</v>
+      </c>
+      <c r="C168" s="57">
+        <v>26817000</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E168" s="14">
+        <v>33994421</v>
+      </c>
+      <c r="F168" s="11">
+        <v>35216900</v>
+      </c>
+      <c r="G168" s="95">
+        <f t="shared" si="2"/>
+        <v>3.4712850932364862E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B169" s="61">
+        <v>25695965</v>
+      </c>
+      <c r="C169" s="57">
+        <v>27189500</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E169" s="14">
+        <v>32384034</v>
+      </c>
+      <c r="F169" s="11">
+        <v>33392900</v>
+      </c>
+      <c r="G169" s="95">
+        <f t="shared" si="2"/>
+        <v>3.0211991171776035E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B170" s="61">
+        <v>25389400</v>
+      </c>
+      <c r="C170" s="57">
+        <v>26374500</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E170" s="14">
+        <v>30695500</v>
+      </c>
+      <c r="F170" s="11">
+        <v>33367000</v>
+      </c>
+      <c r="G170" s="95">
+        <f t="shared" si="2"/>
+        <v>8.0064135223424343E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B171" s="61">
+        <v>25306000</v>
+      </c>
+      <c r="C171" s="57">
+        <v>27042700</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E171" s="14">
+        <v>30244980</v>
+      </c>
+      <c r="F171" s="11">
+        <v>30985800</v>
+      </c>
+      <c r="G171" s="95">
+        <f t="shared" si="2"/>
+        <v>2.3908370931200743E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B172" s="61">
+        <v>24820818</v>
+      </c>
+      <c r="C172" s="57">
+        <v>26336800</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E172" s="14">
+        <v>28691900</v>
+      </c>
+      <c r="F172" s="11">
+        <v>30224000</v>
+      </c>
+      <c r="G172" s="95">
+        <f t="shared" si="2"/>
+        <v>5.0691503440974062E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B173" s="61">
+        <v>23473300</v>
+      </c>
+      <c r="C173" s="57">
+        <v>25487300</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E173" s="14">
+        <v>28023659</v>
+      </c>
+      <c r="F173" s="11">
+        <v>29215000</v>
+      </c>
+      <c r="G173" s="95">
+        <f t="shared" si="2"/>
+        <v>4.0778401506075646E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B174" s="61">
+        <v>23410700</v>
+      </c>
+      <c r="C174" s="57">
+        <v>24987900</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E174" s="14">
+        <v>27595766</v>
+      </c>
+      <c r="F174" s="11">
+        <v>28851800</v>
+      </c>
+      <c r="G174" s="95">
+        <f t="shared" si="2"/>
+        <v>4.3533990946838672E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B175" s="61">
+        <v>22719000</v>
+      </c>
+      <c r="C175" s="57">
+        <v>23129000</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E175" s="14">
+        <v>27500759</v>
+      </c>
+      <c r="F175" s="11">
+        <v>28295000</v>
+      </c>
+      <c r="G175" s="95">
+        <f t="shared" si="2"/>
+        <v>2.8070012369676621E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B176" s="61">
+        <v>17290000</v>
+      </c>
+      <c r="C176" s="57">
+        <v>17480000</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E176" s="14">
+        <v>27286634</v>
+      </c>
+      <c r="F176" s="11">
+        <v>28233000</v>
+      </c>
+      <c r="G176" s="95">
+        <f t="shared" si="2"/>
+        <v>3.3519852654694864E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B177" s="61">
+        <v>14855000</v>
+      </c>
+      <c r="C177" s="57">
+        <v>14855000</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E177" s="14">
+        <v>26601189</v>
+      </c>
+      <c r="F177" s="11">
+        <v>28136000</v>
+      </c>
+      <c r="G177" s="95">
+        <f t="shared" si="2"/>
+        <v>5.4549722775092409E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B178" s="61">
+        <v>14767000</v>
+      </c>
+      <c r="C178" s="57">
+        <v>15037000</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E178" s="14">
+        <v>26121110</v>
+      </c>
+      <c r="F178" s="11">
+        <v>27134800</v>
+      </c>
+      <c r="G178" s="95">
+        <f t="shared" si="2"/>
+        <v>3.7357562981853561E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B179" s="61">
+        <v>14131000</v>
+      </c>
+      <c r="C179" s="57">
+        <v>14251000</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E179" s="14">
+        <v>26039274</v>
+      </c>
+      <c r="F179" s="11">
+        <v>27073900</v>
+      </c>
+      <c r="G179" s="95">
+        <f t="shared" si="2"/>
+        <v>3.8214885923343149E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B180" s="61">
+        <v>13899400</v>
+      </c>
+      <c r="C180" s="57">
+        <v>14341100</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E180" s="14">
+        <v>25786620</v>
+      </c>
+      <c r="F180" s="11">
+        <v>26948800</v>
+      </c>
+      <c r="G180" s="95">
+        <f t="shared" si="2"/>
+        <v>4.3125482396247701E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B181" s="61">
+        <v>13450000</v>
+      </c>
+      <c r="C181" s="57">
+        <v>13470000</v>
+      </c>
+      <c r="D181" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E181" s="14">
+        <v>22539600</v>
+      </c>
+      <c r="F181" s="11">
+        <v>23206900</v>
+      </c>
+      <c r="G181" s="95">
+        <f t="shared" si="2"/>
+        <v>2.8754379085530597E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B182" s="61">
+        <v>12567000</v>
+      </c>
+      <c r="C182" s="57">
+        <v>12567000</v>
+      </c>
+      <c r="D182" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="E182" s="14">
+        <v>22052700</v>
+      </c>
+      <c r="F182" s="11">
+        <v>24246000</v>
+      </c>
+      <c r="G182" s="95">
+        <f t="shared" si="2"/>
+        <v>9.0460282108389009E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B183" s="61">
+        <v>12042000</v>
+      </c>
+      <c r="C183" s="57">
+        <v>12162000</v>
+      </c>
+      <c r="D183" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="E183" s="14">
+        <v>21544249</v>
+      </c>
+      <c r="F183" s="11">
+        <v>22189000</v>
+      </c>
+      <c r="G183" s="95">
+        <f t="shared" si="2"/>
+        <v>2.9057235567172924E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B184" s="61">
+        <v>11096000</v>
+      </c>
+      <c r="C184" s="57">
+        <v>11166000</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="E184" s="14">
+        <v>21224000</v>
+      </c>
+      <c r="F184" s="11">
+        <v>21926900</v>
+      </c>
+      <c r="G184" s="95">
+        <f t="shared" si="2"/>
+        <v>3.2056515056847978E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B185" s="61">
+        <v>9233000</v>
+      </c>
+      <c r="C185" s="57">
+        <v>9233000</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="E185" s="14">
+        <v>15709900</v>
+      </c>
+      <c r="F185" s="11">
+        <v>16726000</v>
+      </c>
+      <c r="G185" s="95">
+        <f t="shared" si="2"/>
+        <v>6.0749730957790266E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B186" s="61">
+        <v>8110000</v>
+      </c>
+      <c r="C186" s="57">
+        <v>8110000</v>
+      </c>
+      <c r="D186" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E186" s="14">
+        <v>15588000</v>
+      </c>
+      <c r="F186" s="11">
+        <v>15588000</v>
+      </c>
+      <c r="G186" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B187" s="61">
+        <v>7319000</v>
+      </c>
+      <c r="C187" s="57">
+        <v>7439000</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E187" s="14">
+        <v>14040000</v>
+      </c>
+      <c r="F187" s="11">
+        <v>14040000</v>
+      </c>
+      <c r="G187" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B188" s="61">
+        <v>6489000</v>
+      </c>
+      <c r="C188" s="57">
+        <v>6489000</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E188" s="14">
+        <v>13824000</v>
+      </c>
+      <c r="F188" s="11">
+        <v>13824000</v>
+      </c>
+      <c r="G188" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B189" s="61">
+        <v>6456000</v>
+      </c>
+      <c r="C189" s="57">
+        <v>6606000</v>
+      </c>
+      <c r="D189" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E189" s="14">
+        <v>12708000</v>
+      </c>
+      <c r="F189" s="11">
+        <v>12708000</v>
+      </c>
+      <c r="G189" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B190" s="61">
+        <v>4866000</v>
+      </c>
+      <c r="C190" s="57">
+        <v>4866000</v>
+      </c>
+      <c r="D190" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E190" s="14">
+        <v>11376000</v>
+      </c>
+      <c r="F190" s="11">
+        <v>11376000</v>
+      </c>
+      <c r="G190" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B191" s="61">
+        <v>4815000</v>
+      </c>
+      <c r="C191" s="57">
+        <v>4835000</v>
+      </c>
+      <c r="D191" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E191" s="14">
+        <v>10152000</v>
+      </c>
+      <c r="F191" s="11">
+        <v>10152000</v>
+      </c>
+      <c r="G191" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B192" s="61">
+        <v>4707000</v>
+      </c>
+      <c r="C192" s="57">
+        <v>4707000</v>
+      </c>
+      <c r="D192" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E192" s="14">
+        <v>8172000</v>
+      </c>
+      <c r="F192" s="11">
+        <v>8172000</v>
+      </c>
+      <c r="G192" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B193" s="61">
+        <v>4481000</v>
+      </c>
+      <c r="C193" s="57">
+        <v>4481000</v>
+      </c>
+      <c r="D193" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E193" s="14">
+        <v>7884000</v>
+      </c>
+      <c r="F193" s="11">
+        <v>7884000</v>
+      </c>
+      <c r="G193" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B194" s="61">
+        <v>3442000</v>
+      </c>
+      <c r="C194" s="57">
+        <v>3442000</v>
+      </c>
+      <c r="D194" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E194" s="14">
+        <v>7740000</v>
+      </c>
+      <c r="F194" s="11">
+        <v>7740000</v>
+      </c>
+      <c r="G194" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B195" s="61">
+        <v>2672000</v>
+      </c>
+      <c r="C195" s="57">
+        <v>2672000</v>
+      </c>
+      <c r="D195" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="E195" s="14">
+        <v>7416000</v>
+      </c>
+      <c r="F195" s="11">
+        <v>7416000</v>
+      </c>
+      <c r="G195" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B196" s="61">
+        <v>2567000</v>
+      </c>
+      <c r="C196" s="57">
+        <v>2567000</v>
+      </c>
+      <c r="D196" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E196" s="14">
+        <v>5436000</v>
+      </c>
+      <c r="F196" s="11">
+        <v>5436000</v>
+      </c>
+      <c r="G196" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B197" s="61">
+        <v>2340000</v>
+      </c>
+      <c r="C197" s="57">
+        <v>2340000</v>
+      </c>
+      <c r="D197" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E197" s="14">
+        <v>5292000</v>
+      </c>
+      <c r="G197" s="95" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B198" s="61">
+        <v>2326000</v>
+      </c>
+      <c r="C198" s="57">
+        <v>2326000</v>
+      </c>
+      <c r="D198" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E198" s="14">
+        <v>5220000</v>
+      </c>
+      <c r="F198" s="11">
+        <v>5220000</v>
+      </c>
+      <c r="G198" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B199" s="61">
+        <v>2280000</v>
+      </c>
+      <c r="C199" s="57">
+        <v>2280000</v>
+      </c>
+      <c r="D199" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="E199" s="14">
+        <v>4932000</v>
+      </c>
+      <c r="F199" s="11">
+        <v>4932000</v>
+      </c>
+      <c r="G199" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B200" s="61">
+        <v>2245000</v>
+      </c>
+      <c r="C200" s="57">
+        <v>2245000</v>
+      </c>
+      <c r="D200" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E200" s="14">
+        <v>4932000</v>
+      </c>
+      <c r="F200" s="11">
+        <v>4932000</v>
+      </c>
+      <c r="G200" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B201" s="61">
+        <v>1645000</v>
+      </c>
+      <c r="C201" s="57">
+        <v>1645000</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E201" s="14">
+        <v>4860000</v>
+      </c>
+      <c r="F201" s="11">
+        <v>4860000</v>
+      </c>
+      <c r="G201" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B202" s="61">
+        <v>1477000</v>
+      </c>
+      <c r="C202" s="57">
+        <v>1477000</v>
+      </c>
+      <c r="D202" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E202" s="14">
+        <v>4140000</v>
+      </c>
+      <c r="F202" s="11">
+        <v>4140000</v>
+      </c>
+      <c r="G202" s="95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B203" s="61">
+        <v>837000</v>
+      </c>
+      <c r="C203" s="57">
+        <v>837000</v>
+      </c>
+      <c r="D203" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E203" s="14">
+        <v>3780000</v>
+      </c>
+      <c r="F203" s="11">
+        <v>3780000</v>
+      </c>
+      <c r="G203" s="95">
+        <f t="shared" ref="G203:G215" si="3">(F203-E203)/F203</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" s="62"/>
+      <c r="B204" s="62"/>
+      <c r="C204" s="63">
+        <v>5462165500</v>
+      </c>
+      <c r="D204" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E204" s="14">
+        <v>3384000</v>
+      </c>
+      <c r="F204" s="11">
+        <v>3384000</v>
+      </c>
+      <c r="G204" s="95">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205" s="62"/>
+      <c r="B205" s="62"/>
+      <c r="C205" s="63">
+        <v>26816278400</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="E205" s="14">
+        <v>3024000</v>
+      </c>
+      <c r="F205" s="11">
+        <v>3024000</v>
+      </c>
+      <c r="G205" s="95">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C206" s="57">
+        <v>26816278400</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E206" s="14">
+        <v>2556000</v>
+      </c>
+      <c r="F206" s="11">
+        <v>2556000</v>
+      </c>
+      <c r="G206" s="95">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C207" s="57">
+        <v>26816278400</v>
+      </c>
+      <c r="D207" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="E207" s="14">
+        <v>2340000</v>
+      </c>
+      <c r="F207" s="11">
+        <v>2340000</v>
+      </c>
+      <c r="G207" s="95">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D208" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E208" s="14">
+        <v>2340000</v>
+      </c>
+      <c r="F208" s="11">
+        <v>2340000</v>
+      </c>
+      <c r="G208" s="95">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D209" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="E209" s="14">
+        <v>1908000</v>
+      </c>
+      <c r="F209" s="11">
+        <v>1908000</v>
+      </c>
+      <c r="G209" s="95">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D210" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E210" s="14">
+        <v>1908000</v>
+      </c>
+      <c r="F210" s="11">
+        <v>1908000</v>
+      </c>
+      <c r="G210" s="95">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D211" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="E211" s="14">
+        <v>648000</v>
+      </c>
+      <c r="G211" s="95" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="212" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D212" s="12"/>
+      <c r="E212" s="12"/>
+      <c r="F212" s="12">
+        <v>4583990700</v>
+      </c>
+      <c r="G212" s="95">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D213" s="12"/>
+      <c r="E213" s="12"/>
+      <c r="F213" s="12">
+        <v>23090020300</v>
+      </c>
+      <c r="G213" s="95">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F214" s="11">
+        <v>23090020300</v>
+      </c>
+      <c r="G214" s="95">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F215" s="11">
+        <v>23090020300</v>
+      </c>
+      <c r="G215" s="95">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>